--- a/tokopedia-csv/TEMPLATE-ISI-100-PRODUK.xlsx
+++ b/tokopedia-csv/TEMPLATE-ISI-100-PRODUK.xlsx
@@ -11,6 +11,7 @@
     <sheet name="BLOK 1-tempel-C7" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="BLOK 2-tempel-S7" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="BLOK 3-tempel-X7" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="BANTU-KATEGORI" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -430,7 +431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CARA MEMAKAI FILE INI (5 menit)</t>
+          <t>CARA MEMAKAI FILE INI (10 menit)</t>
         </is>
       </c>
     </row>
@@ -447,7 +448,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Anda tinggal COPY-PASTE 3 blok ke file template Tokopedia.</t>
+          <t>Anda tinggal COPY-PASTE 3 blok ke file template Tokopedia (sheet "Template").</t>
         </is>
       </c>
     </row>
@@ -464,113 +465,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Langkah 1 - Isi kolom A (Kategori): klik sel A7, pilih kategori dari panah kecil,</t>
+          <t>Langkah 1 - Isi kolom A (Kategori) PER KELOMPOK (lihat sheet "BANTU-KATEGORI"):</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lalu tarik kotaknya ke bawah sampai baris 106 (klik kotak hijau di sudut sel, tarik ke bawah).</t>
+          <t>contoh: baris 7-36 semuanya treadmill -&gt; klik A7, pilih kategori dari panah kecil,</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pilih kategori yang ada kata Fitness / Gym / Alat Olahraga.</t>
+          <t>lalu tarik kotak hijau di sudut sel ke bawah sampai A36. Ulangi untuk kelompok berikutnya.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Langkah 2 - BLOK 1: buka sheet "BLOK 1-tempel-C7", tekan Ctrl+A (pilih semua), Ctrl+C (copy),</t>
+          <t>Pilih kategori yang paling mirip (ada kata Treadmill / Gym / Fitness / Alat Olahraga).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pindah ke template, klik sel C7, tekan Ctrl+V (paste).</t>
+          <t>Langkah 2 - BLOK 1: buka sheet "BLOK 1-tempel-C7", tekan Ctrl+A (pilih semua), Ctrl+C (copy),</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Langkah 3 - BLOK 2: buka sheet "BLOK 2-tempel-S7", Ctrl+A, Ctrl+C,</t>
+          <t>pindah ke template, klik sel C7, tekan Ctrl+V (paste).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pindah ke template, klik sel S7, Ctrl+V.</t>
+          <t>Langkah 3 - BLOK 2: buka sheet "BLOK 2-tempel-S7", Ctrl+A, Ctrl+C,</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Langkah 4 - BLOK 3: buka sheet "BLOK 3-tempel-X7", Ctrl+A, Ctrl+C,</t>
+          <t>pindah ke template, klik sel S7, Ctrl+V.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pindah ke template, klik sel X7, Ctrl+V.</t>
+          <t>Langkah 4 - BLOK 3: buka sheet "BLOK 3-tempel-X7", Ctrl+A, Ctrl+C,</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Langkah 5 - Di template tekan Ctrl+S (simpan). Upload di Seller Center &gt; Langkah 2.</t>
+          <t>pindah ke template, klik sel X7, Ctrl+V.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Langkah 5 - Di template tekan Ctrl+S (simpan). Upload di Seller Center &gt; Langkah 2 (Unggah File).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CATATAN: kolom B (Merek) dikosongkan - tidak wajib.</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CATATAN 2: 4 baris terakhir (97-100) dimensinya kosong -</t>
+          <t>CATATAN: kolom B (Merek) dan kolom Y (Pre-sale) sengaja dikosongkan - benar begitu.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kalau upload error, hapus saja 4 baris itu di template.</t>
+          <t>CATATAN 2: 4 baris PALING BAWAH dimensinya kosong -</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CATATAN 3: kalau kategori sebuah produk tidak ada di pilihan kolom A,</t>
+          <t>kalau upload error, hapus saja 4 baris paling bawah itu di template.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hapus baris produk itu (di-upload nanti dengan template kategori lain).</t>
+          <t>CATATAN 3: kalau jenis produk tidak ada di pilihan kolom A,</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
+        <is>
+          <t>hapus baris produk itu (di-upload nanti dengan template kategori lain).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Kalau ada foto ditolak Tokopedia, beri tahu saya.</t>
         </is>
@@ -593,490 +601,10 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Rubber Flooring Rubber Tile Uk.50x50cm Tebal 20mm</t>
+          <t>Walking Pad CH-21</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
-        <is>
-          <t>Gym Floor dengan ketebalan 2 cm dirancang khusus untuk memberikan kenyamanan dan perlindungan optimal dalam berbagai aktivitas olahraga dan kebugaran. 
-Gym Floor dengan bahan berkualitas tinggi yang tahan lama, memastikan penggunaan jangka panjang tanpa penurunan performa.
-Spesifikasi :
-Ukuran 50 x 50cm
-Tebal 20mm / 2cm
-Bahan EPDM solid produksi dengan standart berkualitas tinggi dijamin bersih tanpa bau
-Berat per pc : 4kg solid &amp; padat.
-Warna: Hitam (atau pilihan warna lain jika tersedia)
-Kelebihan:
-Memberikan kenyamanan dan perlindungan maksimal
-Tahan lama dan cocok untuk penggunaan intensif
-Permukaan anti-slip untuk keamanan latihan
-Mudah dipasang dan dirawat tidak berpori
-Dapat menciptakan area latihan yang aman, nyaman, dan profesional. Produk ini merupakan investasi ideal untuk siapa saja yang serius dalam menjaga kebugaran dan kesehatan, gym floor kami sangat tahan bahkan terhadap cuaca outdoor sampai 15thn</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/4f8391328a6006c40b6dfd4f85bd08be2d12adba-450x450.jpg</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/6f7f6ed2b826e95071560178766ddb69975bc0da-450x450.jpg</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/15cbfe180e1b6b0c02e8ac52cf43d916ee4c9684-1024x844.jpg</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
-      <c r="K1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Rubber Flooring Rubber Tile Uk.50x50cm Tebal 15mm</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Diskripsi :
-- Warna : Hitam
-- Selain warna hitam bisa chat admin
-- Tebal : 15 mm
-- Ukuran : 50 x 50 cm
-- Anti Slip
-- Pemasangan Mudah
-- Cocok untuk fitness
-- Harga yang tertera adalah harga per lembar</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/995e928cbb1b611c0d0961ea55ab0d51383ecbb9-448x394.jpg</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/fef1c367d2c4dc63cdb3ccf605ce873672fbf0f3-991x967.jpg</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/04301861323d042c0d338489bf387fcf880930e0-1024x711.jpg</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/3e03f98d68413d49e673c5a51bf358f80756de57-687x1024.jpg</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Spon Busa Kaki Alat Fitness</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Spon busa yang biasa digunakan pada alat gym.
-Bahan terbuat dari busa tebal rebonik dilapisi kain kulit imitasi, mudah dibersihkan maupun diganti, sangat kuat standart alat fitness gym  
-Ukuran :
-Panjang : 20cm
-Diameter dalam(lubang) : 2cm
-Dameter luar : 11cm
-Berat : 250gr</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/59d2f7be2d88569a1fdeee79d43a462449e70384-728x800.jpg</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/b228a365de12d05a015ecedc24be0b1cd5effde7-259x441.jpg</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/c2c93a17ce9007c8b2d396538594ce3e830ba665-619x710.jpg</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/df1a74d3ac4062342c51b4b94d524a6f55fe5367-450x317.jpg</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Rubber Flooring Pyramid Puzzle Uk.50x50cm Tebal 10mm</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Rubber Flooring Pyramid Model Puzzle
-Bahan   : Rubber 
-Ukuran  : 50x50cm
-Tebal     : 10mm
-Per meter²  isi 4 pcs 
-Berat 14kg/m2
-Harga yang tertera harga satuan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/04d7e7fa629572443f72d9ae6871f16c21bd1aaa-800x800.jpg</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/9ae81546a348511a43e9d7f8275fe536392d417f-764x764.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Sit Up Bench Total TL-712</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>- TINGKAT KEMIRINGAN DAPAT DISESUIAKAN
-- BANTALAN YANG EMPUK SANGAT MEMBERIKAN KENYAMANAN
-- TERDAPAT BANTALAN PADA KUNCIAN KAKI
-- MAKSIMAL BERAT : 80 Kg
-- DIMENSI KEMASAN : 135 x 16 x 33 Cm
-- DIMENSI PRODUK : 146 x 41 x 66 Cm
-- NW/GW : 8/9 Kg
-- WARNA : MERAH, KUNING, &amp; BIRU</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/2100646fea1cdaefdef206d8e9ce466910c41c61-1440x1440.jpg</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/7788be8faa2d18ab001f8b87784d289ca0a64649-473x490.png</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Figure Trimmer Twister With Rope</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>- 2-in-1 pijat dan alat olahraga
-- Dilengkapi dengan tali
-- Dapat memutar hingga 360 derajat
-- Dilengkapi dengan 8 partikel magnet
-- Terbuat dari bahan plastik yang kuat, tidak mudah pecah atau rusak
-- Diameter 28 cm, Ketebalan 3.1 cm
-- Dapat memutar dua arah
-- Rekomendasi beban maksimal 100 kg
-- Berkualitas sangat baik
-- Dikirim sesuai warna yang ready</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/4668793b7b0558e755899f18534de32c3f5d3be7-300x225.jpg</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/c9402ddf5d08ae1c08027f105c308f99ed1e1fbf-182x180.jpg</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/95258bd988653e529d847f13dc6dbc1a4ee976b0-180x180.jpg</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Matras Senam Lokal</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>- Bahan Spon Rebonit
-- Lapis Kulit Mitasi
-- Uk.50x100cm 
-- Tebal 2cm
-- Standard buat gym</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/36143276282069aef1a29d344c31099a5cc26eaf-800x600.jpg</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/5864bffbc9c1fbc6afb5c87e107f9d1695b0445e-836x1280.jpg</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Dumbell Set Plastik 20kg</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Dumbell Set PVC Merk Total Fitness 
-Isi Paket 20 KG :
-- plat 1,25 kg 4 pcs
-- plat 1,5kg 4 pcs
-- plat 2kg 4 pcs
-- mor pengunci 8 pcs
-• 2 stik pegangan
-• 1 stik penyambung
-Panjang Stick : 41cm
-Panjang Konektor : 40cm
-Panjang Gabungan Stick : 93cm</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/4d3811e5ca583aefa902a41fd15a218c7a73dbcd-500x500.jpg</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/33e867d4761e2c945a2d025a27e688c015fe2d31-800x594.jpg</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AB Machine TL-950</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Monitor menampilkan : waktu, kalori dan jumlah gerakan
-Fungsi : Melatih otot punggung, otot perut, otot lengan, otot paha dan kaki
-Warma : Hitam, Hijau, Ungu
-Dimensi produk : 95 x 40 x 95 cm
-Max pengguna : 100kg
-NW/GW : 11/12 kg</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/aeaea10c8a8bbe3ba4558ecba455af1f351d285a-318x312.png</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/152cd8ac5aa26dd9088ca3f140329e472b240b7f-444x443.png</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/ad412e6ec2461c352687d51b54f81a66f9cadd90-447x336.png</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Stair Climber TL-8200</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Material : PP, Rubber , dan Besi
-- Fungsi : Melatih otot pinggul, otot perut, otot paha dan otot kaki
-- Max berat : 100 KG
-- Dimensi kemasan : 90 x 14 x 50 Cm
-- Dimensi produk : 87 x 49 x 128 cm
-- NW/GW : 11/12,5 KG
-- Warna : Merah, Orange, Biru</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/1cb09f90a5bc900ff718d4b3a46c30e588be7fb1-900x900.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/be092c400b46695aace459dd6d65310a2cd06655-900x900.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/39c9084137cbd9569f916cf08417f70a831aa527-900x900.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sepeda Statis Platinum Bike TL-8207</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Monitor                   : LCD Screen, Timer, Calories, Distance, Speed &amp; Hand Pulse Sensor
-Max Weight             : 125 Kg
-Dimension Product  : 113 x 52 x 149 Cm
-Dimension Box         : 88 x 19 x 59 Cm
-NW / GW                  : 15 / 17 Kg</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/2ca7ae55820726bf63891cf55c6c5eba13ccffa6-1280x1600.jpg</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/b5499acc222c94d7d04713bcde6665376f71e16f-475x487.png</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/bd93559fd30e3014cfbd2cd1376b80835f55102c-495x472.png</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/69dd0df2f9c9ee1b4b2cfe75f51751901d6cc5ee-475x488.png</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sepeda Statis Wind Bike TL-8202</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>- MONITOR	:	LCD LED, WAKTU, KECEPATAN,
-PEGUKUR DETAK JANTUNG
-- FITUR	:	HAND PULSE SENSOR,
-- MAKSIMAL BERAT	:	150 Kg
-- DIMENSI KEMASAN	:	87x 23 x 63 Cm
-- DIMENSI PRODUK	:	102 x 47 x 112 Cm
-- NW/GW	:	18/21 Kg</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/b635ba075f74046af2a87457f64ceb50eba1f996-1280x1600.jpg</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/ac48097affe865759cc5c68f9467e41d1c3bbd2e-485x485.png</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/42f684708f34aaec96075eb2a57ec94b48d17862-492x485.png</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/66c117bc72e63cf60cadef8a7f9942bfe65c0143-482x490.png</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Walking Pad CH-21</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
         <is>
           <t>SPESIFIKASI CH-21
 - Motor : 1,5 HP DC
@@ -1089,35 +617,35 @@
 - NW/GW : 17/21 Kg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/c78b1cc0775bc81421e256b6b73c14b065d3729e-484x466.png</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/12fab948f2cd68cfd6be5419b8597f6835784117-496x478.png</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/40ac87427e747d6101d3a220bcf7699c84752a91-487x493.png</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Walking Pad TL-336</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>- Motor : 1 HP DC
 - Kecepatan : 1.0 - 10 Km/Jam
@@ -1129,157 +657,39 @@
 - NW/GW : 19/22 Kg</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/90bcc29f8d3ce23f5a85952bd78ff64c6db063f7-1282x1600.jpg</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/92374f6075841dbb44a5f9250c95bc9bc1127d8d-400x400.png</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/31533409969d67facb9553714f207144471d0042-398x367.png</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/473ea5cb3ae24f069e145e061cc11b868384ffc1-379x322.png</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Bench Press TL-750</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>- Material : PP , RUBBER , BESI DAN BUSA
-- Fungsi ; Melatih otot punggung , otot kaki , otot perut , otot lengan
-- Dimensi kemasan : 114 x 47 x 20 CM
-- Dimensi produk : 63 x 137 x 125 CM
-- NW/GW : 26,5/28 KG</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/0221cb89ab487625a341b53f708d43ab4c7eb966-450x450.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/87ecd0045ac05e1598fba14e3623a08e6ab04fa6-450x450.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/4f0997987a52c58ea43450c7ffc13326089a6063-450x450.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Sepeda Statis Magnetic TL-8208</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Monitor : LED,LCD,Time,Speed,Hand Pulse  Sensor
-Feature : Hand Pulse Sensor
-Max Weight : 100kg
-Dimenson : 89 x 49 x 119 cm
-Dmension Box : 64 x 26 x 56 cm
-NW/GW : 18/20kg</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/3b251f30035c9b2a2f4d512b56dcd32df9600893-445x447.png</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/05d9cca7bc11e4b1ee709b97e6d4f716165a586e-756x629.jpg</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/996d45b0876f7734a879af58d9bc3a9aba8a23a6-454x436.png</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sepeda Statis Spinning Bike TL-960</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>- MOnitor : LCD LED
-- Roda Besi : 6 kg
-- Max berat pengguna : 110 kg
-- Fitur ; Kalori, Detak Jantung, waktu,kecepatan, Jarak tempuh
-- Dimensi produk : 108 x49 x 128 cm
-- NW/GW : 24/27 kg
-- Warna : Kuning &amp; Merah</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/25485c3d430f172735548171fd63816f90f3631e-403x406.png</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/97670d57f79da5f3ee5370567408880cab57178e-410x400.png</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/7f623908e5901bf5e047f85cde806bac82281a0a-402x406.png</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/f64cc80e60dbf408a166e8b37e3b6efe3d3efa61-348x364.png</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Walking Pad TL-220</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>SPESIFIKASI WALKING PAD TL-220
 Running Belt : 40 x 100 cm
@@ -1292,118 +702,43 @@
 Fungsi Latihan : Burning Calories, Train The Heart</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/a3298cd995d9b250d99c6a03ece539b5f613c599-443x435.png</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/6b7fb6c6e98a51e10be830a656ecbb60f7ada098-438x442.png</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/4cc20a92a691c101f322af67a68493a86e3e6fdb-438x439.png</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/f73307044ec399874fb28b489ebaf611a27f0f3a-442x447.png</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/9b56ee57a6b9aff7e2e930929980d0b94a8ecf7f-442x444.png</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Sepeda Statis Magnetic TL-360B</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Berat Bersih / Kotor	:	23 kg / 25 kg
-Beban Maksimum	:	130 kg
-Dimensi	:	87 x 48 x 130 cm
-Control Tension	:	8 Level Magnetic Resistance
-Monitor	:	Time, Speed, Distance, Calorie, Pulse, ODO
-Garansi	:	12 Bulan Resmi Total Fitness</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/c7c5718c380bf85fd5d52787a20adcd1ddc224c3-1280x1600.jpg</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/97681c070f9652f40b34fd932ca73e288ddef780-440x409.png</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Sepeda Statis Spinning Bike TL-8300 New</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>- Roda besi : 13 Kg
-- Max pengguna : 130 Kg
-- Monitor : Kalori, Detak jantung, Waktu, kecepatan, Jarak tempuh
-- Dimensi produk : 96 x 54 x 120 cm
-- NW/GW : 35/37 Kg</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/b9f16efa30c558dfab101cb8f0ae169f6e29e0b0-1280x1600.jpg</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/2355972a8d9cda2acbfc2871d600e6553f101523-445x454.png</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/957c558232cbb24c284408d62366749c2c5899e0-450x443.png</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/734ded2fb13aaaf1a015dd17275e7cecbb2771ac-434x446.png</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Walking Pad TL-212 2 in 1</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Running Belt : 37 x 107 cm
 Kecepatan : 1.0 – 12 Km/Jam
@@ -1416,193 +751,27 @@
 Fungsi Latihan : Burning Calories, Train The Heart</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/9e3a76bce9ddba8a1e7ec1738b02a26a52449215-1600x1511.jpg</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Sepeda Statis Orbitrack Plat TL-8290</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Spesifikasi sepeda statis orbitrack :
-Dilengkapi dengan monitor Jarak, Kecepatan, Kalori yang dibakar, detak jantung, dan waktu tempuh
-Berat maksimal pengguna sampai 120 Kg.
-Dilengkapi dengan pemberat gir untuk gerakan ringan, sedang dan berat.
-Dilengkapi dengan twister untuk melatih pinggang
-Dilengkapi dengan 2 dumble 2kg dan 2 dumble 3 kg
-Assembly Size: 98 x 22 x 71 cm.
-+ / – level resistance.
-Carton Orbitrack Size: 98 x 22 x 66.5 cm.
-Carton Twister Size: 47 x 7 x 27 cm.</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/12a0cd996150f0cd1c66e39bb6f2485bf2dbd11e-487x488.png</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/d29e20548702e3a81ce70521169ea00f65ef9bf8-493x478.png</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/b68eba95f81cc3c3a5697e4743f300fa6c51644a-477x486.png</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/2665cc0cfab6b5524b22912534a84e74d14bb665-336x343.jpg</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Sepeda Statis Recumbent TL-368R</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Model	:	TL-368R (Ultimate Series – AXIONMOVE)
-Tipe	:	Recumbent Magnetic Bike (sepeda statis duduk bersandar)
-NW / GW	:	27 kg / 30 kg
-Beban Maksimum	:	130 kg
-Dimensi	:	138 x 67 x 118 cm
-Control Tension	:	8 Level Magnetic Resistance
-Monitor	:	Time, Speed, Distance, Calorie, Pulse, ODO
-Garansi	:	12 Bulan Resmi Total Fitness</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/6e0206e814b8251dbf44ecc3cfb1072d416638b7-1280x1600.jpg</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/6bf76cd0732d1c1e0dd173cf25f2350b151f1416-439x405.png</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Home Gym 1sisi TL-HG-009 Beban 75kg</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>- Dimensi produk : 165 x 95 x 202 cm
-- Lempengan beban : 75 Kg
-- Fungsi : Butterfly, Chest press, Pull dwon, Bicep, Leg Curl, Tricep, Rope
-- NW/GW : 132/135 Kg</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/1c152033e2877b9a965f4ba66b49ac23f200af3e-448x457.png</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/904c077dfdd6b239d18eed8848cb3f05514016a3-436x410.png</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/88846208dd7ec16afec504efaf6acab4899691e1-434x448.png</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/e3dfb88a5cee98c86c242e6b72238bbceaf6198a-445x458.png</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Recumbent Bike Commercial CMR</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>- Monitor : LCD LED. Kalori, Detak Jantung, Waktu, Kecepatan, Jarak tempuh
-- Rangka : Pipa Baja
-- Sistem Rem : Magnet
-- Sistem Penggerak : Belt
-- Max Berat Pengguna : 150 Kg
-- Dimensi produk : 158 x 61 x 141 cm
-- NW/GW : 60/74 Kg
-- Warna : Hitam</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/092e6e9639359261f783818a93ae59815e5ff193-480x488.png</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/5b645e9bd8510c7cfa349051743146cdb2a3926c-506x477.png</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/122327ce809860d3e3be9066cc99f8b318add37f-466x483.png</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/eebfa250f701a2b2d34e9e357b94ec3601198a55-369x367.png</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Treadmill Commercial Manual Curve TL-800</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Monitor : LCG, Waktu, Kalori, Jarak Tempuh, Kecepatan
 Running Material : ABS Rubber
@@ -1612,179 +781,39 @@
 NW/GW : 150/190 kg</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/f07e4ed48f761a4d7847fa8a17c3250c3ff1c849-1280x1600.jpg</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/abd671459f22e92d47f023c1e28ca543b93538ed-491x490.png</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/ccee534e2cc413cf2f857a31234aa2c39ea00a39-495x470.png</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/e27c16dd2a5b43b0b6daaacfb6dddb1780edbcb0-478x485.png</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Elliptical Crosstrainer Magnetic Bike TL-366E</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>- Monitor : Time, Speed, Distance, calori, Pulse
-- Max pengguna : 130 Kg
-- Dimensi produk : 115 x 63 x 154 cm
-- Control Tension : 8 Level
-- NW/GW : 31/35 kg</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/5320ce6a86b1283870e17a5f84daf06f323cc271-1280x1600.jpg</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/958509d4c11c0916f7141ba1c11a1b78c8abec07-441x411.png</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Home Gym 1sisi TL-HG-006</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>- Dimension : 170 x 90 x 210 cm
-- Weight Stack : 75 Kg
-- Function : Triceps pushdown,Lat Pulldown,Leg ext,Butterfly,Standing Leg Curl,Vertical Chest press,AB Crunch,Bicep Curl,Pec Fly,Rowing</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/6b5b6bae803e28293be60d6b1cdcacc5a927a505-1280x1600.jpg</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/a49495a6a93814a2791a6f4c800a36007826eb29-1599x1600.jpg</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/88846208dd7ec16afec504efaf6acab4899691e1-434x448.png</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Double Handle Solid / Handle Row BM-A238</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Seated Row Handle
-Grade : Komersial Use
-Material : Besi chrome solid
-Grip : Rubber
-Ukuran : 18.5 x 14 x 12 cm
-Berat : 1.9kg</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/1b7cf79400ac0016fc3d34542cef64b1cbd1fda9-1024x907.jpg</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/06c153e5defc53369ca0d41b58d90eee8084d0f8-900x784.jpg</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Sepeda Statis X-Bike TL-925</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>- Rangka : Pipa besi
-- Max pengguna : 100 Kg
-- Dimensi produk : 78 x 40 x 104 cm
-- Dimensi kemasan : 115 x 42 x 21 cm
-- NW/GW : 17/19 Kg
-- Warna : Hitam, Orange</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/a3833e457866b1e85f7766ad844291d04e44dd8b-491x492.png</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/666c4960a51d41537acff83f0473b0d0ddd12f7c-485x460.png</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/8e296cea7051935350cc6d8cbe67423b59286cb6-483x484.png</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Treadmill Walking Pad TL-111 Portable</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>- Motor : 1,5 HP DC
 - Kecepatan : 1.0 - 10 Km/Jam
@@ -1796,352 +825,39 @@
 - NW/GW : 28/32 Kg</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/3d395d84beb2fe501bd4520a2fe8cb9a8fc4c4ea-1280x1600.jpg</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/cebb36048841c04f84523fc0c41d0ada67bc800a-1280x1600.jpg</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/d3189b8f34edd7a456cd0a6e51783bb22bf1cf0e-494x492.png</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/a64cfadd6f31723267f59c944e875a760f2fd702-479x493.png</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Bangku Adjustable Bench TL-1200</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Package Size : 132 X 48 X 30 Cm
-NW/GW : 41/44 Kg</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/93baa6f3f386735b9bea8f48895acd8fe950c4f7-450x450.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/623bed1ab94e54690447b1dbe3b700ac0d094b95-900x900.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/18e15e1b2172749a17d86b6d0baf726f2830cf69-900x900.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Spinning Bike Racer Commercial</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>- Monitor : Shuttle Flying,(Speed, Calories, Distance &amp;APP) Phone &amp; Ipad Holder
-- Flywheel : 15kg
-- Transmission system : Belt
-- Handle : Dipping Hnadle Bar
-- Max User : 125Kg
-- Dimensi Produk : 127 x 64 x 120 cm
-- Dimensi Kemasan : 107 x 20 x 85 cm
-- NW/GW : 43/49 Kg</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/8b416d4d3d9a1826c20e80e736cfbab86c5a33f2-409x406.png</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/57434e42d63b104f171013efc51759f4c454ab70-409x399.png</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/91e52859bfb852afa6f0276f65c8a105c5050602-402x407.png</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Home Gym 1sisi TL-HG-011 Weight Stack 75kg</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Dimensi: 200 x 120 x 210 cm
-Beban (Weight Stack): 75 Kg
-Frame Tube: 40 x 80 mm
-Garansi: 12 bulan resmi Total Fitness
-Tipe: Home Gym All-in-One</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/f4365c616ce66547b4a441ffb4272967eadb9e1e-1280x1600.jpg</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/579c1153b996fd91c3ddb063bf271e46eec54c30-438x388.png</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/21a18f660b9f0eeb60bbe2117c517b90babc03ac-381x447.png</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/a31b1759ea67916d2940952b9f1f6e18ff2bdf51-409x424.png</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Home Gym 3sisi + Squat TL-HG-055</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>- Dimension : 190 x 240 x 230 cm
-- Weight Stack : 75 Kg
-- Function : Triceps pushdown,Lat Pulldown,Leg ext,Butterfly,Standing Leg Curl,Vertical Chest press,AB Crunch,Bicep Curl,Pull Up,Chin Up,Squat,Rowing</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/4a42e91835e1a72306441d79d08e6367d70d3b3a-1280x1600.jpg</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/301df394aa8d5071c080ed666b1d606f9c4458cd-1600x1599.jpg</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Smith Machine MultiGym TL-099 ( Free Rubber Plate 40kg )</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>- Dimensi produk : 210 x 170 x 225 cm
-- Weight Stack : 150kg
-- Fungsi : High Pulling,Low Pulling,Chest Fly,Preacher Squat,Abdominal,Butterfly,Chest Press,Squat,Rowing,Leg Press
-- Color : Black &amp; Red</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/0a4bca8b293d07dc86c0cf95901a0fb3b71d304e-1600x1600.jpg</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/c63256cd2eeb190348bc645263881f60a0b6bd58-1600x1600.jpg</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/ed6b6852c5da2287d2f494aaec926de99b1ddb88-2132x2560.jpg</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/16dc629b1151dbddf6a2722137101555410dfed2-2406x2560.jpg</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Bosu Balance Ball Bola Gym</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Fitur Utama:
-Sangat Fleksibel – Mudah digunakan untuk berbagai gerakan olahraga 
-Permukaan Anti Selip – Memberikan cengkeraman optimal 
-Material Berkualitas – Kokoh dan tahan lama
-Multifungsi – Ideal untuk yoga, pilates, latihan keseimbangan
-Spesifikasi
-- Motif : Random
-- Bahan : Karet Plastik PVC
-- Diameter : 58 Cm x T 20 Cm 
-- Size Paket : P 60 X L 12 X  T 50</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/041dab5856653a5c72d102d9137513a69d3df226-800x800.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/feac9207ef48e9a890d4e3db2d357d84c8f30498-1024x1024.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/834420e333555963e7661eadb9cc58edb6e3f297-1024x1024.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Dumbell Bench TL-1202</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>- Fungsi : Sit Up &amp; Rope
-- Fitur : Incline, Dicline Dan Flat
-- Buku Panduan Manual
-- Maksimal Berat : 100 Kg
-- Dimensi Produk : 120 X 43 X 97 Cm
-- Dimensi Kemasan : 31 X 27 X 123 Cm
-- Nw/gw : 12/13 Kg</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/2662ac78ccf24fadc2813f6851ca3ad697a60b9d-500x500.jpg</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/ba224084b5c0815859fa79908c76b8e787744f30-900x900.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/5f7ff3e41b8ce0f9d4b2c2aab6315380cb8b13a8-900x900.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/c0994c73ccb69b2a3cbf4e0ed82e0c5a1a1d9cdf-900x900.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/3df5d0bbe2911db459f6717f93dffd420191aaf2-1024x1024.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Elliptical Crosstrainer Magnetic Bike Tl-8505</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Monitor : LED,LCD,Timer,Speed,Pulse Sensor, Calory Burning Sensor
-Feature : Hand Pulse Sensor
-Max Weight : 110Kg
-Dimension : 116 x 49 x 115 cm
-Dmension Box : 89 x 25 x 52 cm
-NW/GW  : 31/34 kg</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/56c861746833fbc05bdfbe04fb65ae036dd26a2c-493x494.png</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/6ecbf71a050a7574a628484d673d5db6f17d0012-501x482.png</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/e1f45c0019f9828e45b9ed308edbc69abae7c5a5-494x485.png</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-629</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>- Motor	:	1,5 HP DC
 - Kecepatan	:	1.0 - 12 Km/Jam
@@ -2155,35 +871,35 @@
 - NW/GW	:	27/36 Kg</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/60be3338f2e773c8d8e8dbb5f89e6a561f9dec04-441x444.png</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/bd8729571cda38954fe3e7f496958b8f2699b7f2-409x403.png</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/7f73d7e8e79c6cf688b04a2d7981852d46db8a26-406x408.png</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-266</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>- Motor : 1,5HP DC
 - Kecepatan : 1.0 - 14 Km/Jam
@@ -2197,35 +913,35 @@
 - NW/GW : 34/43 Kg</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/670b7404d40212b5e7e2286d142b3bf76716f380-311x391.png</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/58d7914237c1ca058dd26c191b1f65f441a09f2b-449x448.png</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/04fde103a7024714faa84ded4a580765156c2724-452x446.png</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Treadmill Electric Tl-246</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Motor Power	:	DC 1,5HP
 - Monitor	:	LCD , Detak jantung, Waktu, Calori, Jarak Tempuh, Distance, kecepatan
@@ -2241,39 +957,39 @@
 - NW/GW	:	33/39Kg</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/dfbc896f9499f6273a795469c14ce948bcaca02d-413x419.png</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/1430a7b7ecf0d4cadd1add86822bfb2983433c2c-419x416.png</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/1d306210c50f9a3af0a20bc7c620ec47d7f7042f-418x415.png</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/9fa309518204b22dc0031bc8ad25708b9607b917-351x392.png</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Treadmill Electric Tl-607</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Spesifikasi
 . Motor	:	DC 1.5 HP
@@ -2292,35 +1008,35 @@
 - Expand Size	:	133,5cm x 66cm x 119cm</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/f256d7a5377ee32eac748cce074855b623f725b8-442x445.png</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/679bebe7fe500233c93c1e072c07ad981af4952f-487x495.png</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/090a25387649d395703bcbb582d1c6a26e426d57-487x494.png</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-130</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Spesifikasi :
 - Motor : 2.0hp DC Motor
@@ -2337,35 +1053,35 @@
 - Box Dimension : 171 x 73 x 28 cm</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/84080ca466e7fba869616dd01fc5679106a0c59d-1280x1600.jpg</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/7cb6e492842221512b788242311b97dfb80a9b7b-447x446.png</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/e60f6b44c27b8f5a2a66ba175cb941a3699e1f93-450x456.png</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Treadmill Walking Pad TL-555 Auto Incline Motor 2HP</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Fitur Unggulan:
 15 Program Otomatis (P1–P15) sesuai kebutuhan latihan
@@ -2380,39 +1096,39 @@
 - Max Beban	:	110 Kg</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/42c47f19cd56ddb8c44fdda735bf2f78bcd17859-1280x1600.jpg</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/a580a09efd71d79c2a5d0e0b258353d59b1818d0-402x402.png</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/e72f4ec73a4ae4d98b8d89650834f5a7c08a4fb3-410x350.png</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/14c397caad7c83263a6b537a68aa40d810654ddf-381x319.png</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-299</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Monitor Lengkap	:	Waktu, Kecepatan, Jarak, Kalori, Bluetooth Music, USB Type-C &amp; Speaker
 ✅ Program Latihan	:	P1 – P12 + Body Fat Test
@@ -2424,39 +1140,39 @@
 ✅ Fungsi Tambahan	:	Massage &amp; Sit Up</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/fca4ed3700e0e8e23c3a61387ec2e98afd5291fc-443x448.png</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/656b5d87be57277197bf1730999a469295fbb2c5-442x441.png</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/91b91a2ac17c1b31574f3a447b8606d29a758c0c-442x443.png</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/7ff232f6aec9f10c8f5dd52bd879c4ef959289d1-446x449.png</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-625</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>-Motor	:	2 hp DC Motor
 -Speed	:	1.0 - 14.0 km/h
@@ -2472,39 +1188,39 @@
 -Box Dimension	:	154 x 76 x 26 cm</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/1583243b730d27dccf792147a95307cfcb04af23-447x450.png</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/907d74c7f5d9ac13e9d957c26383eb09cac15382-437x447.png</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/e3b39209265fbf8ec7a989c3becb1ed7711482e1-446x445.png</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/d1a5e0ee4bf8b4c82fc0a9c5a50d8ecce3852980-444x447.png</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-777</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Monitor Digital: Menampilkan Heart Rate, Time, Speed, Calories &amp; Distance
 Automatic Incline 1–15 untuk variasi intensitas latihan
@@ -2516,35 +1232,35 @@
 Compatible with FitShow App – pantau hasil latihan langsung dari smartphone</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/6c3bd50ed4201e3769fe93076fc31bf74edde855-340x357.png</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/eca44efb74f542de6be0392e8105f029c04bbe0f-419x392.png</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/fd65798f0235eaec9532b8a45232bb53f1aeccbc-315x339.png</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-633</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Kecepatan: 1.0–14 km/jam
 Daya Motor: DC 2HP
@@ -2553,39 +1269,39 @@
 Maksimum Beban: 120 kg</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/6f56d6bfb598d3419610c50c4751d3b21f8db5de-440x604.jpg</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/587d3e49acb611566aee06fd0ed58f6f2bf1409b-443x446.png</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/212144b37a538fba1d49f2b4826b7e5360984c84-445x443.png</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/62d2107bf0b56b2a5580eff779427d5f935c093d-435x446.png</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-270</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>- Motor : 2 HP
 - Kecepatan : 0,8 - 12 km
@@ -2596,35 +1312,35 @@
 - Hand pulse &amp; handle kecepatan pada pegangan tangan</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/9b5eeba8c9564cd62f8fb4413534caebbafa8de6-396x408.png</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/01355ccbbee836d2b4d379d5deb6685d9567c13b-417x403.png</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/f5d8e0d617edff9ab42423c72288ea270763280f-404x404.png</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-680</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Motor      :   2hp  DC Motor
 Speed      :  8-14 km/h
@@ -2640,35 +1356,35 @@
 Box Dimension :  1690 x 760 x 325 MM</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/86569ce644eb56acb38d07c65d3bc68ad1874ee8-406x410.png</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/c24d334b8df59884f7299ffb6faba2012622a076-421x393.png</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/9829da8a7bb7027e722a06e0e1d6a872c2b0a6f4-395x402.png</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-66</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>- Motor : DC 2,5HP
 - Kecepatan : 1.0 - 16.0 Km/h
@@ -2685,43 +1401,43 @@
 - NW/GW : 60/70 Kg</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/904c60a445ce7bc8aa9cd3e0d95e6fb3e46b8187-445x447.png</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/3fb0003d5abc2aae15a75f3a2442382eba9d6155-442x448.png</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/bcc9e8ff8b87c5b715af9726037a36f36d07a554-406x408.png</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/ab0f721870a2bb9c429bbdce39da1abc905902a8-412x402.png</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/2c9d17941061ab4d9548bec3d5b7ad562ceea0fd-408x487.png</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-333</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>SPESIFIKASI TREADMILL TL-333
 - Motor : DC 2,5HP
@@ -2738,39 +1454,39 @@
 - Dilengkapi : Auto refill oil</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/7d7fe7c9b235ad1ec6aac81334adc56de49a9fb4-1280x1600.jpg</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/4f88c3355bcd1d17ec0dad4af9ff21cb8f0b107e-490x488.png</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/4e97a68cf0710e6d9bc3320d5b5cfbd66d24b2eb-501x489.png</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/aab1173c2cc5d6def2b4a26b8429afb4364c442e-468x487.png</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-146</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>- Motor : DC 2,5HP
 - Kecepatan : 1.0 - 20.0 Km/h
@@ -2784,39 +1500,39 @@
 - NW/GW : 71/79 kg</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/7e670ad0e9dd1a372620252c417ea038cc057b83-1280x1600.jpg</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/b5148912101bd058ac76f1eb7fe863883ef9e94c-493x488.png</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/e25a315f542d6d9eaea3a3246408c66e6fd23cec-479x486.png</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/5e4426d9d5bca16941cc768d812906847d474a39-473x493.png</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Treadmill Electric Tl-170 Motor DC</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Spesifikasi:
 Ukuran Running Belt: 135 x 48 cm
@@ -2826,80 +1542,43 @@
 Fungsi: Membakar kalori, melatih jantung, memperkuat otot</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/c9134ee79738123b349183ba1850f2d92b896e74-308x387.png</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/b9dceb0b3843912af0dcb5576d8350a32de53f85-365x332.png</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/c1f8a2715e4cc90c664ee9e8e5422288b0ef9bd7-315x338.png</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/a5467289e8a5fa502eb4763a5b7be89e6bd89e46-299x390.png</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/ef5552ebf42373a42c3b456e14d0588d36887eda-308x388.png</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Dumbell Set Hexagonal 1-10kg + Rack</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/dd542751ae964538765b319e7138ff43c3902b22-756x688.jpg</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/ec4a47c5f128839a67b7c046a3e4bd53337ad179-500x500.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/256e466641edb0f5ee6bd638f9d7810ed3598a55-900x900.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/70a88d0b3866b1c7fb989e8fd4b86d832f5dd6b9-1280x1280.jpg</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/ca9c60854b194f5417fe7249f95c5474f6958a81-1280x1280.jpg</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-198 Motor 4HP</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>- Motor : 4HP DC
 - Kecepatan : 1.0 - 22 Km/jam
@@ -2912,31 +1591,31 @@
 - Program : P1 - P12</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/2db35c02df550e81fb526535802e475858116018-1280x1600.jpg</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/6e6a0258866493bc7f451ed737d645b58dcc3e5a-1600x1511.jpg</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-122 Motor DC 3HP</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>- Motor : 3HP DC
 - Kecepatan : 1.0 - 20 Km/jam
@@ -2952,39 +1631,39 @@
 - Warna : Merah &amp; Silver</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/7569ac181dd9f7a3965baac5af0a848c08bc8ab9-311x386.png</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/f468b81b904848207a2747e97fb2ca714229fc11-485x489.png</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/1bb216a90dc8a1b0ec001e473cf11afe0b8043d1-478x486.png</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/7df0b07e29ee4616a55c740aab1db0ec2dc0301f-475x490.png</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-188 Motor 3HP</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Motor : 3 HP DC Motor
 Speed : 1-18 km/h
@@ -3001,132 +1680,39 @@
 Box Dimension : 187 x 86 x 37 cm</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/af8b301913b3642d019b849691f1c992d30ee26e-1280x1600.jpg</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/5ed6c23496e8f6d6ced092e4d88c0133ddcd9c88-408x411.png</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/7c86617912d833a7cc76683f1f226ace47b3dfa4-419x404.png</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/20adaef87f4d2815869d7c94fa8cdc2f6e166ab7-397x405.png</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Magnetic Bike Commercial CMB</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>- Monitor : LCD LED. Kalori, Detak Jantung, Waktu, Kecepatan, Jarak tempuh
-- Rangka : Pipa Baja
-- Sistem Rem : Magnet
-- Sistem Penggerak : Belt
-- Max Berat Pengguna : 150 Kg
-- Dimensi produk : 118 x 63 x 148 cm
-- NW/GW : 50/59 Kg
-- Warna : Hitam</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/c8cd78a708f309e1c2d5eb34881489db4bad04c4-488x491.png</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/64a7df03adef41c11e6eb8515e442929d4d34ca9-499x488.png</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/05e7c8759928eea0032a4b2488a4d00f84a585f6-476x486.png</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Hip Thrust U3092 DHZ</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Hip Thrust focuses on the glute muscles and simulates the most popular free weight glute training paths. Ergonomic pelvic pads provide secure and comfortable support for training start and end. The traditional bench is replaced by a wide back pad, which greatly reduces the pressure on the back and improves the comfort and stability.
-Dimension : 110 x 131 x 188 cm
-Weight Stack : 95kg
-Features : Large Foot Platform, More Focused, Weight Plate Storage</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/67830966196c4ee60be1729975b1b679797b567b-750x750.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Lat Pull Down 2 Seat Total Fitness</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Dimensi : 210x70x200cm</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/c2fe6f50f01c8cf02460c15da07f0d022b63f62d-718x1080.jpg</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-55AC Motor 4HP</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>SPESIFIKASI TL-55 AC
 - Motor : AC 4 HP
@@ -3140,405 +1726,27 @@
 - Connect Aplikasi Fitshow</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/7b6cca2f923fa031d8a7cf5b04bc1f660c0ce1b4-438x400.png</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>MultiGym PowerRack TL-022</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Fungsi : Smith Machine, Chin up, Sit Up, Cable Crossover, Lat Pull Down, Rowing Machine,Bicep,Tricep dll
-Dimensi produk : 136 x 152 x 209 cm</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/5c0cb0b4a496dee2e8d37ce77033de826fc11914-485x489.png</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/6386226d12b570d50dc1b71c7be82d1c1d652962-485x467.png</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/eb10cb4fa0255c29b7222bbff716052551ec39a4-477x491.png</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Abdominal Isolator U3073C DHZ</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Abdominal Isolators adopt a walk-in and minimalist design without excessive adjustments. The uniquely designed seat pad provides strong support and protection during training. The rollers provide effective cushioning for movement. Counter balanced weight provides a low start resistance to ensure exercise is perfomed smoothly and safety. Elevated footrests provide exercisers with additional support . further enhancing training stabillity and comfort.
-Dimension : 130 x 89 x 162 cm
-Weight Stack : 95kg
-Features : Ergonomic Seat Pad, An Effective Core Workout, Helpful Guidan</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/1e23749818709435a51489294496d1a96d3aa057-750x750.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Lat Pull Down U3012C DHZ</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Platinum Series Pulldown not only can it be used as a part of t series modular core of a plug-in workstation or a multiperson station,but it is also can be used as an independent lat pull down de[vice. The pulley on the Pulldown is located so that users can make the movement in front of the head smoothly. The thigh pad adjustment accommpdates a wide variety of users, and the replaceable handle allows users to practice with different accessories.
-Dimension : 193 x 121 x 234 cm
-Weight : 235 Kg
-Weight Stack : 110</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/c2112ddf20554d91353bf61561b83c7a80b10cfe-301x380.png</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Leg Extention U3002 DHZ</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Leg Extension have multiple starting positions, which can be adjusted freels according to user needs to improve exercise flexibility. The adjustable ankle pad allows the user to choose the most comfotable posture in a small area. The adjustable back cushion alows the knees to be easily aligned with the pivot axis to achieve good biomechanics.
-Dimension : 144 x 103 x 163 cm
-Weight : 230kg
-Weight Stack : 110kg
-Features : Seat Angle, Adjustable Start Position, Ensures Proper Alignment</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/0a1e949141657f7d82ca8609c3eb3a24e6ad9618-750x750.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Leg Press U3003C DHZ</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Platinum Series of Leg Press have widened foot pads. To achieve a better training effect, the design allows full extension during exercises, and support maintaining verticality to simulate a squat exercises. The adjustable seat back can provide different users with their desired starting positions.
-Dimension : 209 x 104 x 163 cm
-Weight : 250 Kg
-Weight Stack : 109 Kg</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/b97e24ac9ba818403ccb0404752a2acea64c9809-398x368.png</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Rotary Torso U3018C DHZ</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Rotary Torso is a powerful and comfortable device that provides users with an effective way to strengthen the core and back muscles. The kneeling position design is adopted, which can stretch the hip flexors while reducing the pressure on the lower back as much as possible. The Uniquely designed knee pads ensure the stability and comfort of use and provide protection for multi-posture training.
-Dimension : 110 x 112 x 163 cm
-Weight : 169kg
-Weight Stack : 65kg
-Features : Oversized Handlebar, Comfortable Pads, Helpful Guidance</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/0eb8d8fa3d10397d2cbe6a5c2b4482473bee533a-750x750.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Shoulder Press U3006C DHZ</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Platinum Series Shoulder Press use a decline back pad with an adjustable seat to better stabilize the torso while adapting to users of different sizes. Simulate shoulder press to better realize shoulder biomechanics. The divice is also equipped with comfortable handles with different posotions, which increases the comfort of exercises and the variety of exercises.
-Dimension : 183 x 133 x 163 cm
-Weight : 236 kg
-Weight Stack : 110 kg</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/eee2825d202465460d6246c4eeddf07ac5bcd595-536x530.png</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Vertical Row U3034C DHZ</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Vertical Press has a comfortable and large multi-position grip, which increases the user's training comfort and training variety. The power-assisted footrest design replaces the traditional adjustable back pad, which can change the starting position of training according to the habits of different customers, and buffer at the end of training.
-Dimension : 155 x 132 x 160 cm
-Weight : 227kg
-Weight Stack : 95kg
-Features : L-Shaped Handles, Adjustments, Helpful Guidance</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/631f37fef460801ebfe5c2b37c55b731acfa0432-750x750.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Long Pull U3033C DHZ</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Longpull not only can it be used as a part of the seriel modular core of a plug-in workstation or a multi-person station, but it is also can be used as an independent mid row device. The LongPull has a raised seat for convenient entry and exit. Separate foot pad can adapt to users of different body types without obstructing the motion path of the device. The mid-row position allows users to maintain an upright back position. Handles are easily interchangeable.
-Dimension : 180 x 133 x 204 cm
-Weight : 215kg
-Weight Stack : 110kg
-Features : Handle Platform, Double Enterance Design, Focus Experience</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/977073e6d19eafaf30a3247dff594d36397ee455-750x750.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Prone Leg Curl U3001C DHZ</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Prone Leg Curl uses a prone design to enhance the ease-of-use experience. The widened elbow pads and grips help users to better stabilize the torse, and the ankle roller pads can be adjusted according to different leg lengths and ensure stable and optimal resistance.
-Dimension : 144 x 103 x 163 cm
-Weight : 230kg
-Weight Stack : 110kg
-Feature : Biomechanical Design, Buffer System, Focus on Experience
-Inquiry Form</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/f26917a3232ea373377c9913d9e9125aa3f5ce8e-750x750.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Abductor &amp; Adductor U3021C DHZ</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Platinum Series Abductor and Adductor features an easy-adjust start position for both inner and outer thigh exercises. Dual foot pegs accommodate a wide range of exercisers. The pivoting thigh pads are angled for improved function and comfort during workouts, making it easier for exercisers to focus on miscle strength.
-Dimension : 161 x 92 x 163 cm
-Weight : 235 Kg
-Weight Stack : 92 kg</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/fa4776978e10f6be173fc6532403db96b5a53f6d-392x373.png</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Lat &amp; Pulley Machine U3085C DHZ</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Platinum Series Lat &amp; Pulley Machine is a dual-fuction machine with lat pulldown and mid-row exercise position. It features an easy-to-adjust thighhold down pad, extended seat and foot bar to facilitate both exercises. Without leaving the seat, you can quickly switch to another training through simple adjustment to maintain training continuity.
-Dimension : 197 x 135 x 224 cm
-Weight : 244 kg
-Weight Stack : 110 kg</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/25f15a4a4ceb63a8e205b74dad4c27f81a52ee4e-396x440.png</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Leg Extention &amp; Leg Curl U3086C DHZ</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Leg extension / Leg Curl is a dual-function machine. Designed with convenient shin pad and ankle pad, you can easily adjust from the sitting positions. The shin pad, located below the knee, is designed to help the leg curl, thereby helping find the correct training position for different exercises.
-Dimension : 144 x 102 x 163 cm
-Weight : 255kg
-Weight Stack : 110kg
-Features : Easy Enterance and Exit, Sitting Adjustment, The Balanced Arm
-Inquiry Form</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/650f8c9554142442dfb1cdf682f4c32d1a152986-750x750.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-99AC Motor 4HP</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Spesifikasi:
 - Motor Power : AC 4 HP
@@ -3553,300 +1761,31 @@
 - Warna : Hitam</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/227a3252140f874ee051548e32ca4756d702d79f-309x388.png</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/eef055d7164d5c4f30a8c5eae52c6d062b2b26fd-428x392.png</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Vertical Press U3008C DHZ</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Platinum Series Vertical Press is great for training upper body muscle groups. The adjustable back pad is used to provide starting position, which balaced both comfort and performance. The split-type motion design allows exercisers to choose a variety of training programs. The low pivot of the movement arm ensures proper path of motion and easyentrance/exit to and from the unit
-Dimension : 148 x 105 x 181 cm
-Weight : 242 Kg
-Weight Stack : 110 Kg</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/b882486bcfd74e316a76f2018b6e70a609b37777-360x397.png</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Chest &amp; Shoulder Press U3084C DHZ</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Platinum Series Chest Shoulder Press realizes the integration of the functions of the three machines into one. On this machine, the user can adjust the pressing arm and seat on the machine to perform bench press, upward oblique press and shoulder press. The comfortable oversized handles in multiple positions, combined with the simple adjustment of tha seat, allow users to easily sit in position for different exercises.
-Dimension : 181 x 146 x 183 cm
-Weight : 256 Kg
-Weight Stack : 110 Kg</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/59da06bdd174d5673bf1938aa2d0d04fb0ebb6de-387x357.png</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Pec Delt / Pec Fly U3007C DHZ</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Platinum Series Rear Delt/pec fly is designed with adjustable rotating arms, which is designed to adapt to the arm lenght of different exercises and provide the correct training posture. The independent adjustment cranksets on both sides not only provide different starting positions, but also make exercise variety. The long and narrow back pad can provide back support for Pec Fly and chest support for the deltoid muscle.
-Dimension : 124 x 99 x 211 cm
-Weight : 249 Kg
-Weight Stack : 110 Kg</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/531359334329bf952f5b948aeede0942b12d4319-332x392.png</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>MultiGym Power Rack TL-026 ( Weight Stack Platik 150kg )</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>- Dimensi produk : 202 x 205 x 222 cm
-- Ketebalan tabung : 3 mm
-- Lempengan beban : 75kg x 2 = 150kg
-- Fungsi : Smith Machine, Chin up,sit up,cable crossover,lat pull down,rowing machine,bicep,tricep,leg press dll
-- NW/GW : 408/460kg</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/4c27ca1c03940af8ab482ace0c6e26baf4543280-494x494.png</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/836976569bc39b4961a57edac711070ff57d8018-497x488.png</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/3d4882d984842bcf961e8256082d5dd586c59474-470x490.png</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Super Squat U3065 DHZ</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Super Squat offers both forward and reverse squat training modes to activate the major muscles of the thighs and hips. The wide , angled foot platform keeps the users path of motion on an incline plane, greatly releasing pressure on the spine. The locking lever will automatically drop when you start training and can be easily reset by pedaling when you exit.
-Weight :  165kg
-Dimension : 231 x 107 x 204 cm
-Features : Dual Training Posture , More Focused , Weight Plate Storage</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/504f6f41946c28e7ab15dbd801da3b99fa8e078a-750x794.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>MultiGym Power Rack TL-026 ( Weight Stack Besi 150kg )</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>- Dimensi produk : 202 x 205 x 222 cm
-- Ketebalan tabung : 3 mm
-- Lempengan beban : 75kg x 2 = 150kg
-- Fungsi : Smith Machine, Chin up,sit up,cable crossover,lat pull down,rowing machine,bicep,tricep,leg press dll
-- NW/GW : 408/460kg</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/4c27ca1c03940af8ab482ace0c6e26baf4543280-494x494.png</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/836976569bc39b4961a57edac711070ff57d8018-497x488.png</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/3d4882d984842bcf961e8256082d5dd586c59474-470x490.png</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Angled Leg Press Linear Bearing U3056S DHZ</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Platinum Series Leg Pressfeatures heavy duty commercial linear bearings for smooth motion and dutable. Th 45-degree angle and two starting positions simulate an optimal leg-pressure movement, but with spinal pressure removed. The ergonomically optimized seat design provides accurates nody positioning and support, the four weight horms on the footplate allow users to easily load the wright plates.
-Dimension : 217 x 161 x 126 cm
-Weight : 241 Kg</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/35da959c0d416be0a9a3b3c43fe2207cc0db434b-420x356.png</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Smith Machine U3063 DHZ</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Platinum Series Smith Machine is popular among users as an innovative, stylish and safe plate loaded machine. The vertical motion of the smith bar provides a stable path to assist exercisers in achieving the correct squat. Multiple locking positions allow users stop training by rotating the smith bar at any point during process of the exercise and acushioned base on the bottom protects the machine from damage caused by a sudden drop of the load bar.
-Dimension : 109 x 218 x 232 cm
-Weight : 258 Kg</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/50c72ac25ccb10274f1bdac55e6b45a21a0aab6e-392x414.png</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Standing Multi Flight U2046 DHZ</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Variable strength device for shoulder and chest exercises while standing, strength arms adjustable in height and limited by angle sdjustment. Safe design and constant weight load compared to dumbbells
-Dimension : 143 x 89 x 199 cm
-Weight : 322kg
-Weight Stack : 80kg
-Features : C-Shapes Grips, Easy to Start, Easy Enterance and Exit</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/23069954598b2ce5952d3527a7bc0b72743f155f-750x750.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-33TT AC Motor 4HP</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>- Motor : AC 4 HP
 - Speed : 1 - 22 Km/Jam
@@ -3857,107 +1796,35 @@
 - NW/GW : 119/131 Kg</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/a4e811a59e8a63e48b777a3449553563a065fee6-486x493.png</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/aa332b57a10b4aad087f3cf05bc8705447af678f-482x488.png</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/7fec5227f51ca95ee3c1b3b47258c32a815e7a57-399x405.png</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Functional Trainer Evost U1017C DHZ</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Platinum Series Functional Trainer support taller users for diverse workouts, with 21 adjustable cable positions to accomodate most users of all sizes, making it even better when as astandalone device. The double 95kg weight stack provides enough load even for experienced lifters.
-Dimension : 156 x 120 x 216 cm
-Weight : 360 Kg
-Weight Stack : 95kg x 2</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/f925994cbf7708ec708441d8c0375ea757948cd8-371x397.png</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Commercial Stair Climber</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>- Monitor : LCD LED. Kalori, Detak Jantung, Waktu, Jarak tempuh, Kecepatan
-- Rangka : Baja Karbon
-- Sistem Rem : Magnet
-- Max Berat Pengguna : 150 Kg
-- Dimensi produk : 142 x 81 x 240 cm
-- Dimensi kemasan : 135 x 95 x 130 cm
-- NW/GW : 205/255 Kg
-- Warna : Hitam</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/e5741d7b52f58fc1b125f471022977b78ba000dc-1280x1600.jpg</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/db104ebd87c9788ac83a036c37a1f09045b34cb4-490x493.png</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/87e906849b54e3ece2c640800c15264252a64df1-503x489.png</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/0fb91608027b2e8c9375b565c1c9cc1ebf229b32-471x487.png</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-88AC Motor 4HP</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Deskripsi
 - Motor : AC 4 HP Peak 7HP Continous Power
@@ -3973,63 +1840,35 @@
 - Warna : Hitam dan Silver</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/78734b39fbea3396601052dd0bf1824d0bf483ee-1280x1600.jpg</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/c53f14e208086ed53b1b2863c6ba024fa3d5cd1e-495x490.png</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/6d8f33b0f39a43e8c7054b6931fbcddfb9e15e27-487x490.png</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Cable Cross Over Evost U3016 DHZ</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Platinum Series Adjustable Crossover is a self-contained cable crossover device that provides two sets of adjustable cable positions allowing two users to execute different workouts at the same time or individually. Supplied with a rubber-wrapped pull-up handle with dual grip positions. With quick and easy adjustments, users can use it alone or in combination with gym benches and other accessories to complete a variety of workouts.
-Dimension : 450 x 109 x 231 cm
-Weight : 411 Kg
-Weight Stack : 95 kg x 2</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/99beb51a1773790d14217b7889fc1c8d96b612e6-452x352.png</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Treadmill Electric TL-26AC Motor 6HP</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Deskripsi
 - Touch screen
@@ -4042,39 +1881,746 @@
 - NW/GW : 164/205 Kg</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/bafcc28b6271f4adaf0b623e6813bdfe122ec661-1282x1600.jpg</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/edb96e7957c15526cb1fa6699e6529ab5558b9f5-401x409.png</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/f918d215e907b3cdcd5353a5e156650489e45c7f-398x399.png</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/6fbb1fb39ecd4205597ef895e4aaa54b0922791d-400x407.png</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Smith Machine MultiGym TL-099 ( Free Rubber Plate 40kg )</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>- Dimensi produk : 210 x 170 x 225 cm
+- Weight Stack : 150kg
+- Fungsi : High Pulling,Low Pulling,Chest Fly,Preacher Squat,Abdominal,Butterfly,Chest Press,Squat,Rowing,Leg Press
+- Color : Black &amp; Red</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/0a4bca8b293d07dc86c0cf95901a0fb3b71d304e-1600x1600.jpg</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/c63256cd2eeb190348bc645263881f60a0b6bd58-1600x1600.jpg</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/ed6b6852c5da2287d2f494aaec926de99b1ddb88-2132x2560.jpg</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/16dc629b1151dbddf6a2722137101555410dfed2-2406x2560.jpg</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Hip Thrust U3092 DHZ</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Hip Thrust focuses on the glute muscles and simulates the most popular free weight glute training paths. Ergonomic pelvic pads provide secure and comfortable support for training start and end. The traditional bench is replaced by a wide back pad, which greatly reduces the pressure on the back and improves the comfort and stability.
+Dimension : 110 x 131 x 188 cm
+Weight Stack : 95kg
+Features : Large Foot Platform, More Focused, Weight Plate Storage</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/67830966196c4ee60be1729975b1b679797b567b-750x750.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Abdominal Isolator U3073C DHZ</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Abdominal Isolators adopt a walk-in and minimalist design without excessive adjustments. The uniquely designed seat pad provides strong support and protection during training. The rollers provide effective cushioning for movement. Counter balanced weight provides a low start resistance to ensure exercise is perfomed smoothly and safety. Elevated footrests provide exercisers with additional support . further enhancing training stabillity and comfort.
+Dimension : 130 x 89 x 162 cm
+Weight Stack : 95kg
+Features : Ergonomic Seat Pad, An Effective Core Workout, Helpful Guidan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/1e23749818709435a51489294496d1a96d3aa057-750x750.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Lat Pull Down U3012C DHZ</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Platinum Series Pulldown not only can it be used as a part of t series modular core of a plug-in workstation or a multiperson station,but it is also can be used as an independent lat pull down de[vice. The pulley on the Pulldown is located so that users can make the movement in front of the head smoothly. The thigh pad adjustment accommpdates a wide variety of users, and the replaceable handle allows users to practice with different accessories.
+Dimension : 193 x 121 x 234 cm
+Weight : 235 Kg
+Weight Stack : 110</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/c2112ddf20554d91353bf61561b83c7a80b10cfe-301x380.png</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Leg Extention U3002 DHZ</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Leg Extension have multiple starting positions, which can be adjusted freels according to user needs to improve exercise flexibility. The adjustable ankle pad allows the user to choose the most comfotable posture in a small area. The adjustable back cushion alows the knees to be easily aligned with the pivot axis to achieve good biomechanics.
+Dimension : 144 x 103 x 163 cm
+Weight : 230kg
+Weight Stack : 110kg
+Features : Seat Angle, Adjustable Start Position, Ensures Proper Alignment</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/0a1e949141657f7d82ca8609c3eb3a24e6ad9618-750x750.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Leg Press U3003C DHZ</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Platinum Series of Leg Press have widened foot pads. To achieve a better training effect, the design allows full extension during exercises, and support maintaining verticality to simulate a squat exercises. The adjustable seat back can provide different users with their desired starting positions.
+Dimension : 209 x 104 x 163 cm
+Weight : 250 Kg
+Weight Stack : 109 Kg</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/b97e24ac9ba818403ccb0404752a2acea64c9809-398x368.png</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Rotary Torso U3018C DHZ</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Rotary Torso is a powerful and comfortable device that provides users with an effective way to strengthen the core and back muscles. The kneeling position design is adopted, which can stretch the hip flexors while reducing the pressure on the lower back as much as possible. The Uniquely designed knee pads ensure the stability and comfort of use and provide protection for multi-posture training.
+Dimension : 110 x 112 x 163 cm
+Weight : 169kg
+Weight Stack : 65kg
+Features : Oversized Handlebar, Comfortable Pads, Helpful Guidance</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/0eb8d8fa3d10397d2cbe6a5c2b4482473bee533a-750x750.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Shoulder Press U3006C DHZ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Platinum Series Shoulder Press use a decline back pad with an adjustable seat to better stabilize the torso while adapting to users of different sizes. Simulate shoulder press to better realize shoulder biomechanics. The divice is also equipped with comfortable handles with different posotions, which increases the comfort of exercises and the variety of exercises.
+Dimension : 183 x 133 x 163 cm
+Weight : 236 kg
+Weight Stack : 110 kg</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/eee2825d202465460d6246c4eeddf07ac5bcd595-536x530.png</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Vertical Row U3034C DHZ</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Vertical Press has a comfortable and large multi-position grip, which increases the user's training comfort and training variety. The power-assisted footrest design replaces the traditional adjustable back pad, which can change the starting position of training according to the habits of different customers, and buffer at the end of training.
+Dimension : 155 x 132 x 160 cm
+Weight : 227kg
+Weight Stack : 95kg
+Features : L-Shaped Handles, Adjustments, Helpful Guidance</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/631f37fef460801ebfe5c2b37c55b731acfa0432-750x750.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Long Pull U3033C DHZ</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Longpull not only can it be used as a part of the seriel modular core of a plug-in workstation or a multi-person station, but it is also can be used as an independent mid row device. The LongPull has a raised seat for convenient entry and exit. Separate foot pad can adapt to users of different body types without obstructing the motion path of the device. The mid-row position allows users to maintain an upright back position. Handles are easily interchangeable.
+Dimension : 180 x 133 x 204 cm
+Weight : 215kg
+Weight Stack : 110kg
+Features : Handle Platform, Double Enterance Design, Focus Experience</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/977073e6d19eafaf30a3247dff594d36397ee455-750x750.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Prone Leg Curl U3001C DHZ</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Prone Leg Curl uses a prone design to enhance the ease-of-use experience. The widened elbow pads and grips help users to better stabilize the torse, and the ankle roller pads can be adjusted according to different leg lengths and ensure stable and optimal resistance.
+Dimension : 144 x 103 x 163 cm
+Weight : 230kg
+Weight Stack : 110kg
+Feature : Biomechanical Design, Buffer System, Focus on Experience
+Inquiry Form</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/f26917a3232ea373377c9913d9e9125aa3f5ce8e-750x750.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Abductor &amp; Adductor U3021C DHZ</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Platinum Series Abductor and Adductor features an easy-adjust start position for both inner and outer thigh exercises. Dual foot pegs accommodate a wide range of exercisers. The pivoting thigh pads are angled for improved function and comfort during workouts, making it easier for exercisers to focus on miscle strength.
+Dimension : 161 x 92 x 163 cm
+Weight : 235 Kg
+Weight Stack : 92 kg</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/fa4776978e10f6be173fc6532403db96b5a53f6d-392x373.png</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Lat &amp; Pulley Machine U3085C DHZ</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Platinum Series Lat &amp; Pulley Machine is a dual-fuction machine with lat pulldown and mid-row exercise position. It features an easy-to-adjust thighhold down pad, extended seat and foot bar to facilitate both exercises. Without leaving the seat, you can quickly switch to another training through simple adjustment to maintain training continuity.
+Dimension : 197 x 135 x 224 cm
+Weight : 244 kg
+Weight Stack : 110 kg</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/25f15a4a4ceb63a8e205b74dad4c27f81a52ee4e-396x440.png</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Leg Extention &amp; Leg Curl U3086C DHZ</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Leg extension / Leg Curl is a dual-function machine. Designed with convenient shin pad and ankle pad, you can easily adjust from the sitting positions. The shin pad, located below the knee, is designed to help the leg curl, thereby helping find the correct training position for different exercises.
+Dimension : 144 x 102 x 163 cm
+Weight : 255kg
+Weight Stack : 110kg
+Features : Easy Enterance and Exit, Sitting Adjustment, The Balanced Arm
+Inquiry Form</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/650f8c9554142442dfb1cdf682f4c32d1a152986-750x750.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Vertical Press U3008C DHZ</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Platinum Series Vertical Press is great for training upper body muscle groups. The adjustable back pad is used to provide starting position, which balaced both comfort and performance. The split-type motion design allows exercisers to choose a variety of training programs. The low pivot of the movement arm ensures proper path of motion and easyentrance/exit to and from the unit
+Dimension : 148 x 105 x 181 cm
+Weight : 242 Kg
+Weight Stack : 110 Kg</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/b882486bcfd74e316a76f2018b6e70a609b37777-360x397.png</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Chest &amp; Shoulder Press U3084C DHZ</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Platinum Series Chest Shoulder Press realizes the integration of the functions of the three machines into one. On this machine, the user can adjust the pressing arm and seat on the machine to perform bench press, upward oblique press and shoulder press. The comfortable oversized handles in multiple positions, combined with the simple adjustment of tha seat, allow users to easily sit in position for different exercises.
+Dimension : 181 x 146 x 183 cm
+Weight : 256 Kg
+Weight Stack : 110 Kg</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/59da06bdd174d5673bf1938aa2d0d04fb0ebb6de-387x357.png</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Pec Delt / Pec Fly U3007C DHZ</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Platinum Series Rear Delt/pec fly is designed with adjustable rotating arms, which is designed to adapt to the arm lenght of different exercises and provide the correct training posture. The independent adjustment cranksets on both sides not only provide different starting positions, but also make exercise variety. The long and narrow back pad can provide back support for Pec Fly and chest support for the deltoid muscle.
+Dimension : 124 x 99 x 211 cm
+Weight : 249 Kg
+Weight Stack : 110 Kg</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/531359334329bf952f5b948aeede0942b12d4319-332x392.png</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Super Squat U3065 DHZ</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Super Squat offers both forward and reverse squat training modes to activate the major muscles of the thighs and hips. The wide , angled foot platform keeps the users path of motion on an incline plane, greatly releasing pressure on the spine. The locking lever will automatically drop when you start training and can be easily reset by pedaling when you exit.
+Weight :  165kg
+Dimension : 231 x 107 x 204 cm
+Features : Dual Training Posture , More Focused , Weight Plate Storage</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/504f6f41946c28e7ab15dbd801da3b99fa8e078a-750x794.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Angled Leg Press Linear Bearing U3056S DHZ</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Platinum Series Leg Pressfeatures heavy duty commercial linear bearings for smooth motion and dutable. Th 45-degree angle and two starting positions simulate an optimal leg-pressure movement, but with spinal pressure removed. The ergonomically optimized seat design provides accurates nody positioning and support, the four weight horms on the footplate allow users to easily load the wright plates.
+Dimension : 217 x 161 x 126 cm
+Weight : 241 Kg</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/35da959c0d416be0a9a3b3c43fe2207cc0db434b-420x356.png</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Smith Machine U3063 DHZ</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Platinum Series Smith Machine is popular among users as an innovative, stylish and safe plate loaded machine. The vertical motion of the smith bar provides a stable path to assist exercisers in achieving the correct squat. Multiple locking positions allow users stop training by rotating the smith bar at any point during process of the exercise and acushioned base on the bottom protects the machine from damage caused by a sudden drop of the load bar.
+Dimension : 109 x 218 x 232 cm
+Weight : 258 Kg</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/50c72ac25ccb10274f1bdac55e6b45a21a0aab6e-392x414.png</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Standing Multi Flight U2046 DHZ</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Variable strength device for shoulder and chest exercises while standing, strength arms adjustable in height and limited by angle sdjustment. Safe design and constant weight load compared to dumbbells
+Dimension : 143 x 89 x 199 cm
+Weight : 322kg
+Weight Stack : 80kg
+Features : C-Shapes Grips, Easy to Start, Easy Enterance and Exit</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/23069954598b2ce5952d3527a7bc0b72743f155f-750x750.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Functional Trainer Evost U1017C DHZ</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Platinum Series Functional Trainer support taller users for diverse workouts, with 21 adjustable cable positions to accomodate most users of all sizes, making it even better when as astandalone device. The double 95kg weight stack provides enough load even for experienced lifters.
+Dimension : 156 x 120 x 216 cm
+Weight : 360 Kg
+Weight Stack : 95kg x 2</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/f925994cbf7708ec708441d8c0375ea757948cd8-371x397.png</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Commercial Stair Climber</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>- Monitor : LCD LED. Kalori, Detak Jantung, Waktu, Jarak tempuh, Kecepatan
+- Rangka : Baja Karbon
+- Sistem Rem : Magnet
+- Max Berat Pengguna : 150 Kg
+- Dimensi produk : 142 x 81 x 240 cm
+- Dimensi kemasan : 135 x 95 x 130 cm
+- NW/GW : 205/255 Kg
+- Warna : Hitam</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/e5741d7b52f58fc1b125f471022977b78ba000dc-1280x1600.jpg</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/db104ebd87c9788ac83a036c37a1f09045b34cb4-490x493.png</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/87e906849b54e3ece2c640800c15264252a64df1-503x489.png</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/0fb91608027b2e8c9375b565c1c9cc1ebf229b32-471x487.png</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Cable Cross Over Evost U3016 DHZ</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Platinum Series Adjustable Crossover is a self-contained cable crossover device that provides two sets of adjustable cable positions allowing two users to execute different workouts at the same time or individually. Supplied with a rubber-wrapped pull-up handle with dual grip positions. With quick and easy adjustments, users can use it alone or in combination with gym benches and other accessories to complete a variety of workouts.
+Dimension : 450 x 109 x 231 cm
+Weight : 411 Kg
+Weight Stack : 95 kg x 2</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/99beb51a1773790d14217b7889fc1c8d96b612e6-452x352.png</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Smith Machine MultiGym Station Commercial TL-088</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>- Dimensi perakitan : 149 x 220 x 198cm
 - Ketebalan tabung : 3mm
@@ -4084,76 +2630,521 @@
 - Fungsi : Smith Machne, Chin Up, Cable Crossover, Lat Pull Down, Rowing machine, Tricep, Bicep, dll</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/49ce1ec401ede959d9e6c3834888672144c17085-491x487.png</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/c5f92d63a27e4bb5044474e8a9368c7edb7d5fba-479x454.png</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/36467e0cf4caa296b931a669011d0d030eab9710-466x482.png</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Aerobic Step Papan Senam ID-03</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Bahan yang Terbuat dari PVC berkualitas tinggi yang di lapisi dengan bahan karet pada alas dan kaki membuat lebih nyaman ,stabil dan anti-slip.
-Spesifikasi :
-- Mudah Digunakan
-- Kokoh Dan Berkualitas
-- Dimensi :Panjang 90 cm x Lebar 34 cm.
-- Ketinggian bisa di atur 3 level : 15 cm , 20 cm , 25 cm.
-- Warna Hitam
-- Alas anti slip
-- Barang Original Idachi</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/d4febfa6fe9fd811762f88911c8d28adc8e15209-736x736.jpg</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/d6de623b6a39595237e3f17a5e67434381b9ad34-720x720.jpg</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/b75ded8d89acc5031564472fafc33660c39d56c0-450x450.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sit Up Bench Total TL-712</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>- TINGKAT KEMIRINGAN DAPAT DISESUIAKAN
+- BANTALAN YANG EMPUK SANGAT MEMBERIKAN KENYAMANAN
+- TERDAPAT BANTALAN PADA KUNCIAN KAKI
+- MAKSIMAL BERAT : 80 Kg
+- DIMENSI KEMASAN : 135 x 16 x 33 Cm
+- DIMENSI PRODUK : 146 x 41 x 66 Cm
+- NW/GW : 8/9 Kg
+- WARNA : MERAH, KUNING, &amp; BIRU</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/2100646fea1cdaefdef206d8e9ce466910c41c61-1440x1440.jpg</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/7788be8faa2d18ab001f8b87784d289ca0a64649-473x490.png</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AB Machine TL-950</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Monitor menampilkan : waktu, kalori dan jumlah gerakan
+Fungsi : Melatih otot punggung, otot perut, otot lengan, otot paha dan kaki
+Warma : Hitam, Hijau, Ungu
+Dimensi produk : 95 x 40 x 95 cm
+Max pengguna : 100kg
+NW/GW : 11/12 kg</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/aeaea10c8a8bbe3ba4558ecba455af1f351d285a-318x312.png</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/152cd8ac5aa26dd9088ca3f140329e472b240b7f-444x443.png</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/ad412e6ec2461c352687d51b54f81a66f9cadd90-447x336.png</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Stair Climber TL-8200</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Material : PP, Rubber , dan Besi
+- Fungsi : Melatih otot pinggul, otot perut, otot paha dan otot kaki
+- Max berat : 100 KG
+- Dimensi kemasan : 90 x 14 x 50 Cm
+- Dimensi produk : 87 x 49 x 128 cm
+- NW/GW : 11/12,5 KG
+- Warna : Merah, Orange, Biru</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/1cb09f90a5bc900ff718d4b3a46c30e588be7fb1-900x900.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/be092c400b46695aace459dd6d65310a2cd06655-900x900.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/39c9084137cbd9569f916cf08417f70a831aa527-900x900.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Bench Press TL-750</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>- Material : PP , RUBBER , BESI DAN BUSA
+- Fungsi ; Melatih otot punggung , otot kaki , otot perut , otot lengan
+- Dimensi kemasan : 114 x 47 x 20 CM
+- Dimensi produk : 63 x 137 x 125 CM
+- NW/GW : 26,5/28 KG</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/0221cb89ab487625a341b53f708d43ab4c7eb966-450x450.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/87ecd0045ac05e1598fba14e3623a08e6ab04fa6-450x450.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/4f0997987a52c58ea43450c7ffc13326089a6063-450x450.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Home Gym 1sisi TL-HG-009 Beban 75kg</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>- Dimensi produk : 165 x 95 x 202 cm
+- Lempengan beban : 75 Kg
+- Fungsi : Butterfly, Chest press, Pull dwon, Bicep, Leg Curl, Tricep, Rope
+- NW/GW : 132/135 Kg</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/1c152033e2877b9a965f4ba66b49ac23f200af3e-448x457.png</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/904c077dfdd6b239d18eed8848cb3f05514016a3-436x410.png</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/88846208dd7ec16afec504efaf6acab4899691e1-434x448.png</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/e3dfb88a5cee98c86c242e6b72238bbceaf6198a-445x458.png</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Home Gym 1sisi TL-HG-006</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>- Dimension : 170 x 90 x 210 cm
+- Weight Stack : 75 Kg
+- Function : Triceps pushdown,Lat Pulldown,Leg ext,Butterfly,Standing Leg Curl,Vertical Chest press,AB Crunch,Bicep Curl,Pec Fly,Rowing</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/6b5b6bae803e28293be60d6b1cdcacc5a927a505-1280x1600.jpg</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/a49495a6a93814a2791a6f4c800a36007826eb29-1599x1600.jpg</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/88846208dd7ec16afec504efaf6acab4899691e1-434x448.png</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Bangku Adjustable Bench TL-1200</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Package Size : 132 X 48 X 30 Cm
+NW/GW : 41/44 Kg</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/93baa6f3f386735b9bea8f48895acd8fe950c4f7-450x450.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/623bed1ab94e54690447b1dbe3b700ac0d094b95-900x900.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/18e15e1b2172749a17d86b6d0baf726f2830cf69-900x900.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Home Gym 1sisi TL-HG-011 Weight Stack 75kg</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Dimensi: 200 x 120 x 210 cm
+Beban (Weight Stack): 75 Kg
+Frame Tube: 40 x 80 mm
+Garansi: 12 bulan resmi Total Fitness
+Tipe: Home Gym All-in-One</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/f4365c616ce66547b4a441ffb4272967eadb9e1e-1280x1600.jpg</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/579c1153b996fd91c3ddb063bf271e46eec54c30-438x388.png</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/21a18f660b9f0eeb60bbe2117c517b90babc03ac-381x447.png</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/a31b1759ea67916d2940952b9f1f6e18ff2bdf51-409x424.png</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Home Gym 3sisi + Squat TL-HG-055</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>- Dimension : 190 x 240 x 230 cm
+- Weight Stack : 75 Kg
+- Function : Triceps pushdown,Lat Pulldown,Leg ext,Butterfly,Standing Leg Curl,Vertical Chest press,AB Crunch,Bicep Curl,Pull Up,Chin Up,Squat,Rowing</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/4a42e91835e1a72306441d79d08e6367d70d3b3a-1280x1600.jpg</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/301df394aa8d5071c080ed666b1d606f9c4458cd-1600x1599.jpg</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Dumbell Bench TL-1202</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>- Fungsi : Sit Up &amp; Rope
+- Fitur : Incline, Dicline Dan Flat
+- Buku Panduan Manual
+- Maksimal Berat : 100 Kg
+- Dimensi Produk : 120 X 43 X 97 Cm
+- Dimensi Kemasan : 31 X 27 X 123 Cm
+- Nw/gw : 12/13 Kg</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/2662ac78ccf24fadc2813f6851ca3ad697a60b9d-500x500.jpg</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/ba224084b5c0815859fa79908c76b8e787744f30-900x900.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/5f7ff3e41b8ce0f9d4b2c2aab6315380cb8b13a8-900x900.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/c0994c73ccb69b2a3cbf4e0ed82e0c5a1a1d9cdf-900x900.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/3df5d0bbe2911db459f6717f93dffd420191aaf2-1024x1024.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MultiGym PowerRack TL-022</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Fungsi : Smith Machine, Chin up, Sit Up, Cable Crossover, Lat Pull Down, Rowing Machine,Bicep,Tricep dll
+Dimensi produk : 136 x 152 x 209 cm</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/5c0cb0b4a496dee2e8d37ce77033de826fc11914-485x489.png</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/6386226d12b570d50dc1b71c7be82d1c1d652962-485x467.png</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/eb10cb4fa0255c29b7222bbff716052551ec39a4-477x491.png</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MultiGym Power Rack TL-026 ( Weight Stack Platik 150kg )</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>- Dimensi produk : 202 x 205 x 222 cm
+- Ketebalan tabung : 3 mm
+- Lempengan beban : 75kg x 2 = 150kg
+- Fungsi : Smith Machine, Chin up,sit up,cable crossover,lat pull down,rowing machine,bicep,tricep,leg press dll
+- NW/GW : 408/460kg</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/4c27ca1c03940af8ab482ace0c6e26baf4543280-494x494.png</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/836976569bc39b4961a57edac711070ff57d8018-497x488.png</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/3d4882d984842bcf961e8256082d5dd586c59474-470x490.png</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MultiGym Power Rack TL-026 ( Weight Stack Besi 150kg )</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>- Dimensi produk : 202 x 205 x 222 cm
+- Ketebalan tabung : 3 mm
+- Lempengan beban : 75kg x 2 = 150kg
+- Fungsi : Smith Machine, Chin up,sit up,cable crossover,lat pull down,rowing machine,bicep,tricep,leg press dll
+- NW/GW : 408/460kg</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/4c27ca1c03940af8ab482ace0c6e26baf4543280-494x494.png</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/836976569bc39b4961a57edac711070ff57d8018-497x488.png</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/3d4882d984842bcf961e8256082d5dd586c59474-470x490.png</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Bench Press TL-7705</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>– FUNGSI : Bisa digunakan untuk latihan Bench press, Leg curl, Sit Up dan lain sebagainya.
 – MAXSIMAL BEBAN : 100 Kg
@@ -4163,35 +3154,35 @@
 – NW / GW : 27 / 30Kg</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/9505d85a027b2a7502da439b0d2f7bbbfa12f80a-1024x1024.jpg</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/ea6ee8ffccdf5ea2b907f9581a69db47d387e12f-1024x1024.jpg</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>https://cdn.sanity.io/images/856jrik3/production/6412e3500cf74c57310599d774e61d05b9b87cfa-1200x1600.jpg</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Bangku Adjustable Bench B-1500</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>FITUR UNGGULAN:
 3 Posisi Bench: Incline, Flat, Decline
@@ -4205,16 +3196,1033 @@
 Sistem: Adjustable Bench Multi Angle</t>
         </is>
       </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/63f0605cea79f53cfef66281d49da72a3c404390-450x450.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/1f6c0bbc9733db0ad606a9e637d69a6def612444-1024x1024.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Sepeda Statis Platinum Bike TL-8207</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Monitor                   : LCD Screen, Timer, Calories, Distance, Speed &amp; Hand Pulse Sensor
+Max Weight             : 125 Kg
+Dimension Product  : 113 x 52 x 149 Cm
+Dimension Box         : 88 x 19 x 59 Cm
+NW / GW                  : 15 / 17 Kg</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/2ca7ae55820726bf63891cf55c6c5eba13ccffa6-1280x1600.jpg</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/b5499acc222c94d7d04713bcde6665376f71e16f-475x487.png</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/bd93559fd30e3014cfbd2cd1376b80835f55102c-495x472.png</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/69dd0df2f9c9ee1b4b2cfe75f51751901d6cc5ee-475x488.png</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Sepeda Statis Wind Bike TL-8202</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>- MONITOR	:	LCD LED, WAKTU, KECEPATAN,
+PEGUKUR DETAK JANTUNG
+- FITUR	:	HAND PULSE SENSOR,
+- MAKSIMAL BERAT	:	150 Kg
+- DIMENSI KEMASAN	:	87x 23 x 63 Cm
+- DIMENSI PRODUK	:	102 x 47 x 112 Cm
+- NW/GW	:	18/21 Kg</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/b635ba075f74046af2a87457f64ceb50eba1f996-1280x1600.jpg</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/ac48097affe865759cc5c68f9467e41d1c3bbd2e-485x485.png</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/42f684708f34aaec96075eb2a57ec94b48d17862-492x485.png</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/66c117bc72e63cf60cadef8a7f9942bfe65c0143-482x490.png</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Sepeda Statis Magnetic TL-8208</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Monitor : LED,LCD,Time,Speed,Hand Pulse  Sensor
+Feature : Hand Pulse Sensor
+Max Weight : 100kg
+Dimenson : 89 x 49 x 119 cm
+Dmension Box : 64 x 26 x 56 cm
+NW/GW : 18/20kg</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/3b251f30035c9b2a2f4d512b56dcd32df9600893-445x447.png</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/05d9cca7bc11e4b1ee709b97e6d4f716165a586e-756x629.jpg</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/996d45b0876f7734a879af58d9bc3a9aba8a23a6-454x436.png</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sepeda Statis Spinning Bike TL-960</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>- MOnitor : LCD LED
+- Roda Besi : 6 kg
+- Max berat pengguna : 110 kg
+- Fitur ; Kalori, Detak Jantung, waktu,kecepatan, Jarak tempuh
+- Dimensi produk : 108 x49 x 128 cm
+- NW/GW : 24/27 kg
+- Warna : Kuning &amp; Merah</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/25485c3d430f172735548171fd63816f90f3631e-403x406.png</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/97670d57f79da5f3ee5370567408880cab57178e-410x400.png</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/7f623908e5901bf5e047f85cde806bac82281a0a-402x406.png</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/f64cc80e60dbf408a166e8b37e3b6efe3d3efa61-348x364.png</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Sepeda Statis Magnetic TL-360B</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Berat Bersih / Kotor	:	23 kg / 25 kg
+Beban Maksimum	:	130 kg
+Dimensi	:	87 x 48 x 130 cm
+Control Tension	:	8 Level Magnetic Resistance
+Monitor	:	Time, Speed, Distance, Calorie, Pulse, ODO
+Garansi	:	12 Bulan Resmi Total Fitness</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/c7c5718c380bf85fd5d52787a20adcd1ddc224c3-1280x1600.jpg</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/97681c070f9652f40b34fd932ca73e288ddef780-440x409.png</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sepeda Statis Spinning Bike TL-8300 New</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>- Roda besi : 13 Kg
+- Max pengguna : 130 Kg
+- Monitor : Kalori, Detak jantung, Waktu, kecepatan, Jarak tempuh
+- Dimensi produk : 96 x 54 x 120 cm
+- NW/GW : 35/37 Kg</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/b9f16efa30c558dfab101cb8f0ae169f6e29e0b0-1280x1600.jpg</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/2355972a8d9cda2acbfc2871d600e6553f101523-445x454.png</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/957c558232cbb24c284408d62366749c2c5899e0-450x443.png</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/734ded2fb13aaaf1a015dd17275e7cecbb2771ac-434x446.png</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Sepeda Statis Orbitrack Plat TL-8290</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Spesifikasi sepeda statis orbitrack :
+Dilengkapi dengan monitor Jarak, Kecepatan, Kalori yang dibakar, detak jantung, dan waktu tempuh
+Berat maksimal pengguna sampai 120 Kg.
+Dilengkapi dengan pemberat gir untuk gerakan ringan, sedang dan berat.
+Dilengkapi dengan twister untuk melatih pinggang
+Dilengkapi dengan 2 dumble 2kg dan 2 dumble 3 kg
+Assembly Size: 98 x 22 x 71 cm.
++ / – level resistance.
+Carton Orbitrack Size: 98 x 22 x 66.5 cm.
+Carton Twister Size: 47 x 7 x 27 cm.</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/12a0cd996150f0cd1c66e39bb6f2485bf2dbd11e-487x488.png</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/d29e20548702e3a81ce70521169ea00f65ef9bf8-493x478.png</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/b68eba95f81cc3c3a5697e4743f300fa6c51644a-477x486.png</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/2665cc0cfab6b5524b22912534a84e74d14bb665-336x343.jpg</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Sepeda Statis Recumbent TL-368R</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Model	:	TL-368R (Ultimate Series – AXIONMOVE)
+Tipe	:	Recumbent Magnetic Bike (sepeda statis duduk bersandar)
+NW / GW	:	27 kg / 30 kg
+Beban Maksimum	:	130 kg
+Dimensi	:	138 x 67 x 118 cm
+Control Tension	:	8 Level Magnetic Resistance
+Monitor	:	Time, Speed, Distance, Calorie, Pulse, ODO
+Garansi	:	12 Bulan Resmi Total Fitness</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/6e0206e814b8251dbf44ecc3cfb1072d416638b7-1280x1600.jpg</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/6bf76cd0732d1c1e0dd173cf25f2350b151f1416-439x405.png</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Recumbent Bike Commercial CMR</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>- Monitor : LCD LED. Kalori, Detak Jantung, Waktu, Kecepatan, Jarak tempuh
+- Rangka : Pipa Baja
+- Sistem Rem : Magnet
+- Sistem Penggerak : Belt
+- Max Berat Pengguna : 150 Kg
+- Dimensi produk : 158 x 61 x 141 cm
+- NW/GW : 60/74 Kg
+- Warna : Hitam</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/092e6e9639359261f783818a93ae59815e5ff193-480x488.png</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/5b645e9bd8510c7cfa349051743146cdb2a3926c-506x477.png</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/122327ce809860d3e3be9066cc99f8b318add37f-466x483.png</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/eebfa250f701a2b2d34e9e357b94ec3601198a55-369x367.png</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Elliptical Crosstrainer Magnetic Bike TL-366E</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>- Monitor : Time, Speed, Distance, calori, Pulse
+- Max pengguna : 130 Kg
+- Dimensi produk : 115 x 63 x 154 cm
+- Control Tension : 8 Level
+- NW/GW : 31/35 kg</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/5320ce6a86b1283870e17a5f84daf06f323cc271-1280x1600.jpg</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/958509d4c11c0916f7141ba1c11a1b78c8abec07-441x411.png</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Sepeda Statis X-Bike TL-925</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>- Rangka : Pipa besi
+- Max pengguna : 100 Kg
+- Dimensi produk : 78 x 40 x 104 cm
+- Dimensi kemasan : 115 x 42 x 21 cm
+- NW/GW : 17/19 Kg
+- Warna : Hitam, Orange</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/a3833e457866b1e85f7766ad844291d04e44dd8b-491x492.png</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/666c4960a51d41537acff83f0473b0d0ddd12f7c-485x460.png</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/8e296cea7051935350cc6d8cbe67423b59286cb6-483x484.png</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Spinning Bike Racer Commercial</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>- Monitor : Shuttle Flying,(Speed, Calories, Distance &amp;APP) Phone &amp; Ipad Holder
+- Flywheel : 15kg
+- Transmission system : Belt
+- Handle : Dipping Hnadle Bar
+- Max User : 125Kg
+- Dimensi Produk : 127 x 64 x 120 cm
+- Dimensi Kemasan : 107 x 20 x 85 cm
+- NW/GW : 43/49 Kg</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/8b416d4d3d9a1826c20e80e736cfbab86c5a33f2-409x406.png</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/57434e42d63b104f171013efc51759f4c454ab70-409x399.png</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/91e52859bfb852afa6f0276f65c8a105c5050602-402x407.png</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Elliptical Crosstrainer Magnetic Bike Tl-8505</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Monitor : LED,LCD,Timer,Speed,Pulse Sensor, Calory Burning Sensor
+Feature : Hand Pulse Sensor
+Max Weight : 110Kg
+Dimension : 116 x 49 x 115 cm
+Dmension Box : 89 x 25 x 52 cm
+NW/GW  : 31/34 kg</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/56c861746833fbc05bdfbe04fb65ae036dd26a2c-493x494.png</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/6ecbf71a050a7574a628484d673d5db6f17d0012-501x482.png</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/e1f45c0019f9828e45b9ed308edbc69abae7c5a5-494x485.png</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Magnetic Bike Commercial CMB</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>- Monitor : LCD LED. Kalori, Detak Jantung, Waktu, Kecepatan, Jarak tempuh
+- Rangka : Pipa Baja
+- Sistem Rem : Magnet
+- Sistem Penggerak : Belt
+- Max Berat Pengguna : 150 Kg
+- Dimensi produk : 118 x 63 x 148 cm
+- NW/GW : 50/59 Kg
+- Warna : Hitam</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/c8cd78a708f309e1c2d5eb34881489db4bad04c4-488x491.png</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/64a7df03adef41c11e6eb8515e442929d4d34ca9-499x488.png</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/05e7c8759928eea0032a4b2488a4d00f84a585f6-476x486.png</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Figure Trimmer Twister With Rope</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>- 2-in-1 pijat dan alat olahraga
+- Dilengkapi dengan tali
+- Dapat memutar hingga 360 derajat
+- Dilengkapi dengan 8 partikel magnet
+- Terbuat dari bahan plastik yang kuat, tidak mudah pecah atau rusak
+- Diameter 28 cm, Ketebalan 3.1 cm
+- Dapat memutar dua arah
+- Rekomendasi beban maksimal 100 kg
+- Berkualitas sangat baik
+- Dikirim sesuai warna yang ready</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/4668793b7b0558e755899f18534de32c3f5d3be7-300x225.jpg</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/c9402ddf5d08ae1c08027f105c308f99ed1e1fbf-182x180.jpg</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/95258bd988653e529d847f13dc6dbc1a4ee976b0-180x180.jpg</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Matras Senam Lokal</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>- Bahan Spon Rebonit
+- Lapis Kulit Mitasi
+- Uk.50x100cm 
+- Tebal 2cm
+- Standard buat gym</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/36143276282069aef1a29d344c31099a5cc26eaf-800x600.jpg</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/5864bffbc9c1fbc6afb5c87e107f9d1695b0445e-836x1280.jpg</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Double Handle Solid / Handle Row BM-A238</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Seated Row Handle
+Grade : Komersial Use
+Material : Besi chrome solid
+Grip : Rubber
+Ukuran : 18.5 x 14 x 12 cm
+Berat : 1.9kg</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/1b7cf79400ac0016fc3d34542cef64b1cbd1fda9-1024x907.jpg</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/06c153e5defc53369ca0d41b58d90eee8084d0f8-900x784.jpg</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Bosu Balance Ball Bola Gym</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Fitur Utama:
+Sangat Fleksibel – Mudah digunakan untuk berbagai gerakan olahraga 
+Permukaan Anti Selip – Memberikan cengkeraman optimal 
+Material Berkualitas – Kokoh dan tahan lama
+Multifungsi – Ideal untuk yoga, pilates, latihan keseimbangan
+Spesifikasi
+- Motif : Random
+- Bahan : Karet Plastik PVC
+- Diameter : 58 Cm x T 20 Cm 
+- Size Paket : P 60 X L 12 X  T 50</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/041dab5856653a5c72d102d9137513a69d3df226-800x800.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/feac9207ef48e9a890d4e3db2d357d84c8f30498-1024x1024.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/834420e333555963e7661eadb9cc58edb6e3f297-1024x1024.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Aerobic Step Papan Senam ID-03</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Bahan yang Terbuat dari PVC berkualitas tinggi yang di lapisi dengan bahan karet pada alas dan kaki membuat lebih nyaman ,stabil dan anti-slip.
+Spesifikasi :
+- Mudah Digunakan
+- Kokoh Dan Berkualitas
+- Dimensi :Panjang 90 cm x Lebar 34 cm.
+- Ketinggian bisa di atur 3 level : 15 cm , 20 cm , 25 cm.
+- Warna Hitam
+- Alas anti slip
+- Barang Original Idachi</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/d4febfa6fe9fd811762f88911c8d28adc8e15209-736x736.jpg</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/d6de623b6a39595237e3f17a5e67434381b9ad34-720x720.jpg</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/b75ded8d89acc5031564472fafc33660c39d56c0-450x450.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Spon Busa Kaki Alat Fitness</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Spon busa yang biasa digunakan pada alat gym.
+Bahan terbuat dari busa tebal rebonik dilapisi kain kulit imitasi, mudah dibersihkan maupun diganti, sangat kuat standart alat fitness gym  
+Ukuran :
+Panjang : 20cm
+Diameter dalam(lubang) : 2cm
+Dameter luar : 11cm
+Berat : 250gr</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/59d2f7be2d88569a1fdeee79d43a462449e70384-728x800.jpg</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/b228a365de12d05a015ecedc24be0b1cd5effde7-259x441.jpg</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/c2c93a17ce9007c8b2d396538594ce3e830ba665-619x710.jpg</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/df1a74d3ac4062342c51b4b94d524a6f55fe5367-450x317.jpg</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Dumbell Set Plastik 20kg</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Dumbell Set PVC Merk Total Fitness 
+Isi Paket 20 KG :
+- plat 1,25 kg 4 pcs
+- plat 1,5kg 4 pcs
+- plat 2kg 4 pcs
+- mor pengunci 8 pcs
+• 2 stik pegangan
+• 1 stik penyambung
+Panjang Stick : 41cm
+Panjang Konektor : 40cm
+Panjang Gabungan Stick : 93cm</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/4d3811e5ca583aefa902a41fd15a218c7a73dbcd-500x500.jpg</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/33e867d4761e2c945a2d025a27e688c015fe2d31-800x594.jpg</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Dumbell Set Hexagonal 1-10kg + Rack</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/dd542751ae964538765b319e7138ff43c3902b22-756x688.jpg</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/ec4a47c5f128839a67b7c046a3e4bd53337ad179-500x500.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/256e466641edb0f5ee6bd638f9d7810ed3598a55-900x900.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/70a88d0b3866b1c7fb989e8fd4b86d832f5dd6b9-1280x1280.jpg</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/ca9c60854b194f5417fe7249f95c5474f6958a81-1280x1280.jpg</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Rubber Flooring Rubber Tile Uk.50x50cm Tebal 20mm</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Gym Floor dengan ketebalan 2 cm dirancang khusus untuk memberikan kenyamanan dan perlindungan optimal dalam berbagai aktivitas olahraga dan kebugaran. 
+Gym Floor dengan bahan berkualitas tinggi yang tahan lama, memastikan penggunaan jangka panjang tanpa penurunan performa.
+Spesifikasi :
+Ukuran 50 x 50cm
+Tebal 20mm / 2cm
+Bahan EPDM solid produksi dengan standart berkualitas tinggi dijamin bersih tanpa bau
+Berat per pc : 4kg solid &amp; padat.
+Warna: Hitam (atau pilihan warna lain jika tersedia)
+Kelebihan:
+Memberikan kenyamanan dan perlindungan maksimal
+Tahan lama dan cocok untuk penggunaan intensif
+Permukaan anti-slip untuk keamanan latihan
+Mudah dipasang dan dirawat tidak berpori
+Dapat menciptakan area latihan yang aman, nyaman, dan profesional. Produk ini merupakan investasi ideal untuk siapa saja yang serius dalam menjaga kebugaran dan kesehatan, gym floor kami sangat tahan bahkan terhadap cuaca outdoor sampai 15thn</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/4f8391328a6006c40b6dfd4f85bd08be2d12adba-450x450.jpg</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/6f7f6ed2b826e95071560178766ddb69975bc0da-450x450.jpg</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/15cbfe180e1b6b0c02e8ac52cf43d916ee4c9684-1024x844.jpg</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Rubber Flooring Rubber Tile Uk.50x50cm Tebal 15mm</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Diskripsi :
+- Warna : Hitam
+- Selain warna hitam bisa chat admin
+- Tebal : 15 mm
+- Ukuran : 50 x 50 cm
+- Anti Slip
+- Pemasangan Mudah
+- Cocok untuk fitness
+- Harga yang tertera adalah harga per lembar</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/995e928cbb1b611c0d0961ea55ab0d51383ecbb9-448x394.jpg</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/fef1c367d2c4dc63cdb3ccf605ce873672fbf0f3-991x967.jpg</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/04301861323d042c0d338489bf387fcf880930e0-1024x711.jpg</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/3e03f98d68413d49e673c5a51bf358f80756de57-687x1024.jpg</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Rubber Flooring Pyramid Puzzle Uk.50x50cm Tebal 10mm</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Rubber Flooring Pyramid Model Puzzle
+Bahan   : Rubber 
+Ukuran  : 50x50cm
+Tebal     : 10mm
+Per meter²  isi 4 pcs 
+Berat 14kg/m2
+Harga yang tertera harga satuan</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/04d7e7fa629572443f72d9ae6871f16c21bd1aaa-800x800.jpg</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://cdn.sanity.io/images/856jrik3/production/9ae81546a348511a43e9d7f8275fe536392d417f-764x764.webp?fm=jpg</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Lat Pull Down 2 Seat Total Fitness</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Dimensi : 210x70x200cm</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/63f0605cea79f53cfef66281d49da72a3c404390-450x450.webp?fm=jpg</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>https://cdn.sanity.io/images/856jrik3/production/1f6c0bbc9733db0ad606a9e637d69a6def612444-1024x1024.webp?fm=jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.sanity.io/images/856jrik3/production/c2fe6f50f01c8cf02460c15da07f0d022b63f62d-718x1080.jpg</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
@@ -4361,1346 +4369,1346 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>4000</v>
+        <v>21000</v>
       </c>
       <c r="B1" t="n">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="C1" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D1" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3500</v>
+        <v>22000</v>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>500</v>
+        <v>28500</v>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4000</v>
+        <v>27000</v>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9000</v>
+        <v>190000</v>
       </c>
       <c r="B5" t="n">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1000</v>
+        <v>32000</v>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2000</v>
+        <v>36000</v>
       </c>
       <c r="B7" t="n">
-        <v>50</v>
+        <v>136</v>
       </c>
       <c r="C7" t="n">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21000</v>
+        <v>43000</v>
       </c>
       <c r="B8" t="n">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>12000</v>
+        <v>39000</v>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="C9" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="D9" t="n">
-        <v>95</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>12500</v>
+        <v>52000</v>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>17000</v>
+        <v>63000</v>
       </c>
       <c r="B11" t="n">
-        <v>88</v>
+        <v>171</v>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>21000</v>
+        <v>38500</v>
       </c>
       <c r="B12" t="n">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>21000</v>
+        <v>60000</v>
       </c>
       <c r="B13" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>22000</v>
+        <v>54000</v>
       </c>
       <c r="B14" t="n">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>94</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>28000</v>
+        <v>70000</v>
       </c>
       <c r="B15" t="n">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="C15" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20000</v>
+        <v>60000</v>
       </c>
       <c r="B16" t="n">
+        <v>140</v>
+      </c>
+      <c r="C16" t="n">
         <v>64</v>
       </c>
-      <c r="C16" t="n">
-        <v>26</v>
-      </c>
       <c r="D16" t="n">
-        <v>56</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>27000</v>
+        <v>63000</v>
       </c>
       <c r="B17" t="n">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="C17" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D17" t="n">
-        <v>128</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>28500</v>
+        <v>73000</v>
       </c>
       <c r="B18" t="n">
-        <v>125</v>
+        <v>169</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="D18" t="n">
-        <v>105</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>25000</v>
+        <v>70000</v>
       </c>
       <c r="B19" t="n">
-        <v>87</v>
+        <v>169</v>
       </c>
       <c r="C19" t="n">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>130</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>37000</v>
+        <v>72000</v>
       </c>
       <c r="B20" t="n">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="C20" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="D20" t="n">
-        <v>120</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>27000</v>
+        <v>79000</v>
       </c>
       <c r="B21" t="n">
-        <v>122</v>
+        <v>210</v>
       </c>
       <c r="C21" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>115</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>34000</v>
+        <v>99000</v>
       </c>
       <c r="B22" t="n">
-        <v>98</v>
+        <v>170</v>
       </c>
       <c r="C22" t="n">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="D22" t="n">
-        <v>66.5</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="B23" t="n">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="C23" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="D23" t="n">
-        <v>118</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135000</v>
+        <v>93000</v>
       </c>
       <c r="B24" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="C24" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>202</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>74000</v>
+        <v>100000</v>
       </c>
       <c r="B25" t="n">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="C25" t="n">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="D25" t="n">
-        <v>141</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>190000</v>
+        <v>100000</v>
       </c>
       <c r="B26" t="n">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="C26" t="n">
         <v>86</v>
       </c>
       <c r="D26" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>35000</v>
+        <v>105000</v>
       </c>
       <c r="B27" t="n">
-        <v>115</v>
+        <v>175</v>
       </c>
       <c r="C27" t="n">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="D27" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>150000</v>
+        <v>131000</v>
       </c>
       <c r="B28" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="C28" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D28" t="n">
-        <v>210</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2000</v>
+        <v>250000</v>
       </c>
       <c r="B29" t="n">
-        <v>19</v>
+        <v>206</v>
       </c>
       <c r="C29" t="n">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>19000</v>
+        <v>205000</v>
       </c>
       <c r="B30" t="n">
-        <v>115</v>
+        <v>210</v>
       </c>
       <c r="C30" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="D30" t="n">
-        <v>21</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>32000</v>
+        <v>460000</v>
       </c>
       <c r="B31" t="n">
-        <v>126</v>
+        <v>210</v>
       </c>
       <c r="C31" t="n">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="D31" t="n">
-        <v>107</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>44000</v>
+        <v>160000</v>
       </c>
       <c r="B32" t="n">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="C32" t="n">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="D32" t="n">
-        <v>30</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>49000</v>
+        <v>235000</v>
       </c>
       <c r="B33" t="n">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C33" t="n">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="D33" t="n">
-        <v>85</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>145000</v>
+        <v>235000</v>
       </c>
       <c r="B34" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C34" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D34" t="n">
-        <v>210</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>170000</v>
+        <v>230000</v>
       </c>
       <c r="B35" t="n">
-        <v>190</v>
+        <v>144</v>
       </c>
       <c r="C35" t="n">
-        <v>240</v>
+        <v>103</v>
       </c>
       <c r="D35" t="n">
-        <v>230</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>460000</v>
+        <v>250000</v>
       </c>
       <c r="B36" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C36" t="n">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="D36" t="n">
-        <v>225</v>
+        <v>163</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>8000</v>
+        <v>169000</v>
       </c>
       <c r="B37" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="C37" t="n">
-        <v>50</v>
+        <v>112</v>
       </c>
       <c r="D37" t="n">
-        <v>12</v>
+        <v>163</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>13000</v>
+        <v>236000</v>
       </c>
       <c r="B38" t="n">
-        <v>31</v>
+        <v>183</v>
       </c>
       <c r="C38" t="n">
-        <v>27</v>
+        <v>133</v>
       </c>
       <c r="D38" t="n">
-        <v>123</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>34000</v>
+        <v>227000</v>
       </c>
       <c r="B39" t="n">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="C39" t="n">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="D39" t="n">
-        <v>115</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>36000</v>
+        <v>215000</v>
       </c>
       <c r="B40" t="n">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="C40" t="n">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="D40" t="n">
-        <v>106</v>
+        <v>204</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>43000</v>
+        <v>230000</v>
       </c>
       <c r="B41" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C41" t="n">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="D41" t="n">
-        <v>104</v>
+        <v>163</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>39000</v>
+        <v>235000</v>
       </c>
       <c r="B42" t="n">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="C42" t="n">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="D42" t="n">
-        <v>24</v>
+        <v>163</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>52000</v>
+        <v>244000</v>
       </c>
       <c r="B43" t="n">
-        <v>141</v>
+        <v>197</v>
       </c>
       <c r="C43" t="n">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="D43" t="n">
-        <v>29</v>
+        <v>224</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>63000</v>
+        <v>255000</v>
       </c>
       <c r="B44" t="n">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="C44" t="n">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="D44" t="n">
-        <v>28</v>
+        <v>163</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>38500</v>
+        <v>242000</v>
       </c>
       <c r="B45" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="C45" t="n">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="D45" t="n">
-        <v>109</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>60000</v>
+        <v>256000</v>
       </c>
       <c r="B46" t="n">
-        <v>125</v>
+        <v>181</v>
       </c>
       <c r="C46" t="n">
-        <v>56</v>
+        <v>146</v>
       </c>
       <c r="D46" t="n">
-        <v>140</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>54000</v>
+        <v>249000</v>
       </c>
       <c r="B47" t="n">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="C47" t="n">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="D47" t="n">
-        <v>26</v>
+        <v>211</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>70000</v>
+        <v>165000</v>
       </c>
       <c r="B48" t="n">
-        <v>155</v>
+        <v>231</v>
       </c>
       <c r="C48" t="n">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="D48" t="n">
-        <v>122</v>
+        <v>204</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>60000</v>
+        <v>241000</v>
       </c>
       <c r="B49" t="n">
-        <v>140</v>
+        <v>217</v>
       </c>
       <c r="C49" t="n">
-        <v>64</v>
+        <v>161</v>
       </c>
       <c r="D49" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>63000</v>
+        <v>258000</v>
       </c>
       <c r="B50" t="n">
-        <v>171</v>
+        <v>109</v>
       </c>
       <c r="C50" t="n">
-        <v>75</v>
+        <v>218</v>
       </c>
       <c r="D50" t="n">
-        <v>29</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>73000</v>
+        <v>322000</v>
       </c>
       <c r="B51" t="n">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="C51" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="D51" t="n">
-        <v>32.5</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>70000</v>
+        <v>360000</v>
       </c>
       <c r="B52" t="n">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="C52" t="n">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="D52" t="n">
-        <v>33</v>
+        <v>216</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>72000</v>
+        <v>255000</v>
       </c>
       <c r="B53" t="n">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="C53" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D53" t="n">
-        <v>33</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>79000</v>
+        <v>411000</v>
       </c>
       <c r="B54" t="n">
-        <v>210</v>
+        <v>450</v>
       </c>
       <c r="C54" t="n">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="D54" t="n">
-        <v>140</v>
+        <v>231</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>99000</v>
+        <v>460000</v>
       </c>
       <c r="B55" t="n">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="C55" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D55" t="n">
-        <v>147</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130000</v>
+        <v>9000</v>
       </c>
       <c r="B56" t="n">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="C56" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="D56" t="n">
-        <v>150</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>100000</v>
+        <v>12000</v>
       </c>
       <c r="B57" t="n">
-        <v>177</v>
+        <v>95</v>
       </c>
       <c r="C57" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="D57" t="n">
-        <v>143</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>93000</v>
+        <v>12500</v>
       </c>
       <c r="B58" t="n">
-        <v>184</v>
+        <v>90</v>
       </c>
       <c r="C58" t="n">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D58" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>100000</v>
+        <v>28000</v>
       </c>
       <c r="B59" t="n">
-        <v>187</v>
+        <v>114</v>
       </c>
       <c r="C59" t="n">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="D59" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59000</v>
+        <v>135000</v>
       </c>
       <c r="B60" t="n">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="C60" t="n">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="D60" t="n">
-        <v>148</v>
+        <v>202</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>160000</v>
+        <v>150000</v>
       </c>
       <c r="B61" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="C61" t="n">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>188</v>
+        <v>210</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>50000</v>
+        <v>44000</v>
       </c>
       <c r="B62" t="n">
-        <v>210</v>
+        <v>132</v>
       </c>
       <c r="C62" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="D62" t="n">
-        <v>200</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>100000</v>
+        <v>145000</v>
       </c>
       <c r="B63" t="n">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C63" t="n">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="D63" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>189000</v>
+        <v>170000</v>
       </c>
       <c r="B64" t="n">
-        <v>136</v>
+        <v>190</v>
       </c>
       <c r="C64" t="n">
-        <v>152</v>
+        <v>240</v>
       </c>
       <c r="D64" t="n">
-        <v>209</v>
+        <v>230</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>235000</v>
+        <v>13000</v>
       </c>
       <c r="B65" t="n">
-        <v>130</v>
+        <v>31</v>
       </c>
       <c r="C65" t="n">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="D65" t="n">
-        <v>162</v>
+        <v>123</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>235000</v>
+        <v>189000</v>
       </c>
       <c r="B66" t="n">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="C66" t="n">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="D66" t="n">
-        <v>234</v>
+        <v>209</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>230000</v>
+        <v>460000</v>
       </c>
       <c r="B67" t="n">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="C67" t="n">
-        <v>103</v>
+        <v>205</v>
       </c>
       <c r="D67" t="n">
-        <v>163</v>
+        <v>222</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>250000</v>
+        <v>460000</v>
       </c>
       <c r="B68" t="n">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C68" t="n">
-        <v>104</v>
+        <v>205</v>
       </c>
       <c r="D68" t="n">
-        <v>163</v>
+        <v>222</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>169000</v>
+        <v>30000</v>
       </c>
       <c r="B69" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C69" t="n">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="D69" t="n">
-        <v>163</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>236000</v>
+        <v>22000</v>
       </c>
       <c r="B70" t="n">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="C70" t="n">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="D70" t="n">
-        <v>163</v>
+        <v>130</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>227000</v>
+        <v>17000</v>
       </c>
       <c r="B71" t="n">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="C71" t="n">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="D71" t="n">
-        <v>160</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>215000</v>
+        <v>21000</v>
       </c>
       <c r="B72" t="n">
-        <v>180</v>
+        <v>87</v>
       </c>
       <c r="C72" t="n">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="D72" t="n">
-        <v>204</v>
+        <v>63</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>230000</v>
+        <v>20000</v>
       </c>
       <c r="B73" t="n">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="C73" t="n">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="D73" t="n">
-        <v>163</v>
+        <v>56</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>235000</v>
+        <v>27000</v>
       </c>
       <c r="B74" t="n">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="C74" t="n">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="D74" t="n">
-        <v>163</v>
+        <v>128</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>244000</v>
+        <v>25000</v>
       </c>
       <c r="B75" t="n">
-        <v>197</v>
+        <v>87</v>
       </c>
       <c r="C75" t="n">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="D75" t="n">
-        <v>224</v>
+        <v>130</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>255000</v>
+        <v>37000</v>
       </c>
       <c r="B76" t="n">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="C76" t="n">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="D76" t="n">
-        <v>163</v>
+        <v>120</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>105000</v>
+        <v>34000</v>
       </c>
       <c r="B77" t="n">
-        <v>175</v>
+        <v>98</v>
       </c>
       <c r="C77" t="n">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="D77" t="n">
-        <v>158</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>242000</v>
+        <v>30000</v>
       </c>
       <c r="B78" t="n">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C78" t="n">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="D78" t="n">
-        <v>181</v>
+        <v>118</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>256000</v>
+        <v>74000</v>
       </c>
       <c r="B79" t="n">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="C79" t="n">
-        <v>146</v>
+        <v>61</v>
       </c>
       <c r="D79" t="n">
-        <v>183</v>
+        <v>141</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>249000</v>
+        <v>35000</v>
       </c>
       <c r="B80" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C80" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="D80" t="n">
-        <v>211</v>
+        <v>154</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>460000</v>
+        <v>19000</v>
       </c>
       <c r="B81" t="n">
-        <v>202</v>
+        <v>115</v>
       </c>
       <c r="C81" t="n">
-        <v>205</v>
+        <v>42</v>
       </c>
       <c r="D81" t="n">
-        <v>222</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>165000</v>
+        <v>49000</v>
       </c>
       <c r="B82" t="n">
-        <v>231</v>
+        <v>107</v>
       </c>
       <c r="C82" t="n">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="D82" t="n">
-        <v>204</v>
+        <v>85</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>460000</v>
+        <v>34000</v>
       </c>
       <c r="B83" t="n">
-        <v>202</v>
+        <v>116</v>
       </c>
       <c r="C83" t="n">
-        <v>205</v>
+        <v>49</v>
       </c>
       <c r="D83" t="n">
-        <v>222</v>
+        <v>115</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>241000</v>
+        <v>59000</v>
       </c>
       <c r="B84" t="n">
-        <v>217</v>
+        <v>118</v>
       </c>
       <c r="C84" t="n">
-        <v>161</v>
+        <v>63</v>
       </c>
       <c r="D84" t="n">
-        <v>126</v>
+        <v>148</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>258000</v>
+        <v>1000</v>
       </c>
       <c r="B85" t="n">
-        <v>109</v>
+        <v>30</v>
       </c>
       <c r="C85" t="n">
-        <v>218</v>
+        <v>30</v>
       </c>
       <c r="D85" t="n">
-        <v>232</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>322000</v>
+        <v>2000</v>
       </c>
       <c r="B86" t="n">
-        <v>143</v>
+        <v>50</v>
       </c>
       <c r="C86" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D86" t="n">
-        <v>199</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131000</v>
+        <v>2000</v>
       </c>
       <c r="B87" t="n">
-        <v>200</v>
+        <v>19</v>
       </c>
       <c r="C87" t="n">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="D87" t="n">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>360000</v>
+        <v>8000</v>
       </c>
       <c r="B88" t="n">
-        <v>156</v>
+        <v>60</v>
       </c>
       <c r="C88" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="D88" t="n">
-        <v>216</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>255000</v>
+        <v>6000</v>
       </c>
       <c r="B89" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="C89" t="n">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="D89" t="n">
-        <v>130</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>250000</v>
+        <v>500</v>
       </c>
       <c r="B90" t="n">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="C90" t="n">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="D90" t="n">
-        <v>173</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>411000</v>
+        <v>21000</v>
       </c>
       <c r="B91" t="n">
-        <v>450</v>
+        <v>40</v>
       </c>
       <c r="C91" t="n">
-        <v>109</v>
+        <v>25</v>
       </c>
       <c r="D91" t="n">
-        <v>231</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>205000</v>
+        <v>130000</v>
       </c>
       <c r="B92" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="C92" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="D92" t="n">
-        <v>166</v>
+        <v>150</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>460000</v>
+        <v>4000</v>
       </c>
       <c r="B93" t="n">
-        <v>202</v>
+        <v>50</v>
       </c>
       <c r="C93" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D93" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>6000</v>
+        <v>3500</v>
       </c>
       <c r="B94" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="C94" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D94" t="n">
-        <v>25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>30000</v>
+        <v>4000</v>
       </c>
       <c r="B95" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="C95" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D95" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>22000</v>
+        <v>50000</v>
       </c>
       <c r="B96" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="C96" t="n">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="D96" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
     </row>
     <row r="97">
@@ -5751,427 +5759,427 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>95000</v>
+        <v>2000000</v>
       </c>
       <c r="B1" t="inlineStr"/>
       <c r="C1" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>TF-0E2896</t>
+          <t>TF-E2E2C7</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>150000</v>
+        <v>2000000</v>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>TF-195559</t>
+          <t>TF-6DF60B</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130000</v>
+        <v>2550000</v>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TF-012A5B</t>
+          <t>TF-FF6BE4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100000</v>
+        <v>3100000</v>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TF-563EA9</t>
+          <t>TF-276BB9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>600000</v>
+        <v>28000000</v>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TF-4CB35F</t>
+          <t>TF-2C380D</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>150000</v>
+        <v>3390000</v>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TF-3D4924</t>
+          <t>TF-55136E</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>200000</v>
+        <v>3790000</v>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TF-42FFE6</t>
+          <t>TF-0A8A10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>350000</v>
+        <v>3990000</v>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TF-E5C380</t>
+          <t>TF-41FF0B</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>790000</v>
+        <v>4690000</v>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TF-319061</t>
+          <t>TF-8A96EE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>990000</v>
+        <v>4690000</v>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TF-85CF74</t>
+          <t>TF-3C709F</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1550000</v>
+        <v>5280000</v>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TF-B0AAAC</t>
+          <t>TF-011650</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1550000</v>
+        <v>5300000</v>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TF-984BE9</t>
+          <t>TF-895E34</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2000000</v>
+        <v>5550000</v>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TF-E2E2C7</t>
+          <t>TF-F7B84F</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2000000</v>
+        <v>5700000</v>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TF-6DF60B</t>
+          <t>TF-6E703E</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2200000</v>
+        <v>5980000</v>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TF-F50196</t>
+          <t>TF-62F23C</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2480000</v>
+        <v>6380000</v>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TF-CF5869</t>
+          <t>TF-A76A2C</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2480000</v>
+        <v>6790000</v>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TF-951A88</t>
+          <t>TF-CA22A9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2550000</v>
+        <v>7150000</v>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TF-FF6BE4</t>
+          <t>TF-D31752</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2580000</v>
+        <v>7650000</v>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TF-46B6D9</t>
+          <t>TF-BC5919</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3080000</v>
+        <v>8680000</v>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TF-45667E</t>
+          <t>TF-7AC785</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3100000</v>
+        <v>9280000</v>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TF-276BB9</t>
+          <t>TF-906373</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3190000</v>
+        <v>9800000</v>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TF-393CFF</t>
+          <t>TF-113D76</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3350000</v>
+        <v>10800000</v>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TF-8A5222</t>
+          <t>TF-0E58F3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>5690000</v>
+        <v>11200000</v>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TF-CBB7E9</t>
+          <t>TF-C4E840</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>16500000</v>
+        <v>11380000</v>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TF-BC1A5E</t>
+          <t>TF-704386</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>28000000</v>
+        <v>15200000</v>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TF-2C380D</t>
+          <t>TF-D2235B</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3180000</v>
+        <v>18800000</v>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TF-EC3529</t>
+          <t>TF-162734</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5890000</v>
+        <v>26500000</v>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TF-647D15</t>
+          <t>TF-E38508</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>230000</v>
+        <v>28800000</v>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TF-4CB925</t>
+          <t>TF-457392</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2049000</v>
+        <v>39900000</v>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TF-D017FE</t>
+          <t>TF-EDDFE9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3390000</v>
+        <v>32900000</v>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
@@ -6179,83 +6187,83 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>TF-55136E</t>
+          <t>TF-B24C18</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6000000</v>
+        <v>14500000</v>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>TF-4E8A82</t>
+          <t>TF-5BAF33</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6390000</v>
+        <v>17800000</v>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>TF-E56466</t>
+          <t>TF-9BD2F3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>7550000</v>
+        <v>17800000</v>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TF-238453</t>
+          <t>TF-C02ACB</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>10500000</v>
+        <v>17800000</v>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TF-08BD6A</t>
+          <t>TF-1F5A39</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>32900000</v>
+        <v>17800000</v>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TF-B24C18</t>
+          <t>TF-5CD5CF</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>425000</v>
+        <v>17800000</v>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
@@ -6263,13 +6271,13 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>TF-45286A</t>
+          <t>TF-4C9E1B</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>890000</v>
+        <v>17800000</v>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
@@ -6277,13 +6285,13 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>TF-A92F79</t>
+          <t>TF-572C00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3180000</v>
+        <v>17800000</v>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
@@ -6291,13 +6299,13 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>TF-85523E</t>
+          <t>TF-57562D</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3790000</v>
+        <v>18200000</v>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
@@ -6305,13 +6313,13 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>TF-0A8A10</t>
+          <t>TF-4224E5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3990000</v>
+        <v>18300000</v>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
@@ -6319,13 +6327,13 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TF-41FF0B</t>
+          <t>TF-31DE28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>4690000</v>
+        <v>18800000</v>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
@@ -6333,13 +6341,13 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TF-8A96EE</t>
+          <t>TF-FD78E3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4690000</v>
+        <v>18800000</v>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
@@ -6347,13 +6355,13 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TF-3C709F</t>
+          <t>TF-5F669A</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>5280000</v>
+        <v>18800000</v>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
@@ -6361,13 +6369,13 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TF-011650</t>
+          <t>TF-A9CA01</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>5300000</v>
+        <v>18800000</v>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
@@ -6375,13 +6383,13 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TF-895E34</t>
+          <t>TF-3E6926</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>5550000</v>
+        <v>19800000</v>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
@@ -6389,13 +6397,13 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>TF-F7B84F</t>
+          <t>TF-D9C856</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5700000</v>
+        <v>19800000</v>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
@@ -6403,13 +6411,13 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>TF-6E703E</t>
+          <t>TF-30D54E</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>5980000</v>
+        <v>21800000</v>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
@@ -6417,13 +6425,13 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TF-62F23C</t>
+          <t>TF-197529</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>6380000</v>
+        <v>24500000</v>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
@@ -6431,13 +6439,13 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TF-A76A2C</t>
+          <t>TF-C60FB3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>6790000</v>
+        <v>24500000</v>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
@@ -6445,13 +6453,13 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TF-CA22A9</t>
+          <t>TF-AD6880</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>7150000</v>
+        <v>25800000</v>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
@@ -6459,13 +6467,13 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>TF-D31752</t>
+          <t>TF-AD89A5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>7650000</v>
+        <v>26600000</v>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
@@ -6473,13 +6481,13 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TF-BC5919</t>
+          <t>TF-1BAD91</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>8680000</v>
+        <v>28480000</v>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
@@ -6487,13 +6495,13 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>TF-7AC785</t>
+          <t>TF-D13B15</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>9280000</v>
+        <v>30500000</v>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
@@ -6501,13 +6509,13 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>TF-906373</t>
+          <t>TF-AA9C77</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>9800000</v>
+        <v>47000000</v>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
@@ -6515,139 +6523,139 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>TF-113D76</t>
+          <t>TF-7D293E</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>10050000</v>
+        <v>600000</v>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>TF-52C0F7</t>
+          <t>TF-4CB35F</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>10800000</v>
+        <v>790000</v>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>TF-0E58F3</t>
+          <t>TF-319061</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>11200000</v>
+        <v>990000</v>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>TF-C4E840</t>
+          <t>TF-85CF74</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>11380000</v>
+        <v>2200000</v>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>TF-704386</t>
+          <t>TF-F50196</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>12000000</v>
+        <v>5690000</v>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>TF-DD77A4</t>
+          <t>TF-CBB7E9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>14500000</v>
+        <v>5890000</v>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>TF-5BAF33</t>
+          <t>TF-647D15</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>15000000</v>
+        <v>6000000</v>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TF-F81482</t>
+          <t>TF-4E8A82</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>15200000</v>
+        <v>7550000</v>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TF-D2235B</t>
+          <t>TF-238453</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>16590000</v>
+        <v>10500000</v>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TF-98FCF7</t>
+          <t>TF-08BD6A</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>17800000</v>
+        <v>890000</v>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
@@ -6655,13 +6663,13 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TF-9BD2F3</t>
+          <t>TF-A92F79</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>17800000</v>
+        <v>16590000</v>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
@@ -6669,13 +6677,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>TF-C02ACB</t>
+          <t>TF-98FCF7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>17800000</v>
+        <v>21500000</v>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
@@ -6683,13 +6691,13 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>TF-1F5A39</t>
+          <t>TF-9C212C</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>17800000</v>
+        <v>23500000</v>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
@@ -6697,209 +6705,209 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>TF-5CD5CF</t>
+          <t>TF-DBA70E</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>17800000</v>
+        <v>1600000</v>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>TF-4C9E1B</t>
+          <t>TF-318B21</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>17800000</v>
+        <v>2850000</v>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>TF-572C00</t>
+          <t>TF-D46779</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>17800000</v>
+        <v>1550000</v>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>TF-57562D</t>
+          <t>TF-B0AAAC</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>18200000</v>
+        <v>1550000</v>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>TF-4224E5</t>
+          <t>TF-984BE9</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>18300000</v>
+        <v>2480000</v>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>TF-31DE28</t>
+          <t>TF-CF5869</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>18800000</v>
+        <v>2480000</v>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>TF-FD78E3</t>
+          <t>TF-951A88</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>18800000</v>
+        <v>2580000</v>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>TF-5F669A</t>
+          <t>TF-46B6D9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>18800000</v>
+        <v>3080000</v>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>TF-A9CA01</t>
+          <t>TF-45667E</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>18800000</v>
+        <v>3190000</v>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>TF-162734</t>
+          <t>TF-393CFF</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>18800000</v>
+        <v>3350000</v>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>TF-3E6926</t>
+          <t>TF-8A5222</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>19800000</v>
+        <v>16500000</v>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>TF-D9C856</t>
+          <t>TF-BC1A5E</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>19800000</v>
+        <v>3180000</v>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>TF-30D54E</t>
+          <t>TF-EC3529</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>21500000</v>
+        <v>2049000</v>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>TF-9C212C</t>
+          <t>TF-D017FE</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>21800000</v>
+        <v>6390000</v>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>TF-197529</t>
+          <t>TF-E56466</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>23500000</v>
+        <v>3180000</v>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
@@ -6907,13 +6915,13 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>TF-DBA70E</t>
+          <t>TF-85523E</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>24500000</v>
+        <v>12000000</v>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
@@ -6921,55 +6929,55 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>TF-C60FB3</t>
+          <t>TF-DD77A4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>24500000</v>
+        <v>150000</v>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>TF-AD6880</t>
+          <t>TF-3D4924</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>25800000</v>
+        <v>200000</v>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>TF-AD89A5</t>
+          <t>TF-42FFE6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>26500000</v>
+        <v>230000</v>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>TF-E38508</t>
+          <t>TF-4CB925</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>26600000</v>
+        <v>425000</v>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
@@ -6977,55 +6985,55 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>TF-1BAD91</t>
+          <t>TF-45286A</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>28480000</v>
+        <v>450000</v>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>TF-D13B15</t>
+          <t>TF-213C16</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>28800000</v>
+        <v>130000</v>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>TF-457392</t>
+          <t>TF-012A5B</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>30500000</v>
+        <v>350000</v>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>TF-AA9C77</t>
+          <t>TF-E5C380</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>39900000</v>
+        <v>10050000</v>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
@@ -7033,63 +7041,63 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>TF-EDDFE9</t>
+          <t>TF-52C0F7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>47000000</v>
+        <v>95000</v>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>TF-7D293E</t>
+          <t>TF-0E2896</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>450000</v>
+        <v>150000</v>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>TF-213C16</t>
+          <t>TF-195559</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1600000</v>
+        <v>100000</v>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>TF-318B21</t>
+          <t>TF-563EA9</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>2850000</v>
+        <v>15000000</v>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>TF-D46779</t>
+          <t>TF-F81482</t>
         </is>
       </c>
     </row>
@@ -7147,6 +7155,222 @@
         <is>
           <t>TF-66B15D</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Baris di template</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Jenis produk</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Jumlah</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Baris 7-36</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Treadmill &amp; Walking Pad</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Baris 37-61</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Commercial Fitness</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Baris 62-76</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Home Gym &amp; Bench Press</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baris 77-90</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sepeda Statis &amp; Crosstrainer</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baris 91-95</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Stick &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baris 96-96</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sparepart</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Baris 97-98</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dumbell &amp; Weight Plate</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Baris 99-101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rubber Flooring</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Baris 102-102</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fitness Outdoor</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Baris 103-103</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sparepart</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Baris 104-104</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dumbell &amp; Weight Plate</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Baris 105-106</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sparepart</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
